--- a/src/test/resources/manual-testcases-runnable.xlsx
+++ b/src/test/resources/manual-testcases-runnable.xlsx
@@ -1,12 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Login" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Users" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Departments" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Login" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Users" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Team" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Departments" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Resources" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="16">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -85,8 +86,23 @@
     <font>
       <name val="Arial"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -122,8 +138,14 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E9ECEF"/>
+        <bgColor rgb="00E9ECEF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border/>
     <border>
       <left style="thin">
@@ -200,11 +222,25 @@
         <color rgb="FFBFC9D9"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D3D3D3"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -382,6 +418,17 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -34673,4 +34720,3694 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P46"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" style="67" min="1" max="1"/>
+    <col width="16" customWidth="1" style="67" min="2" max="2"/>
+    <col width="30" customWidth="1" style="67" min="3" max="3"/>
+    <col width="16" customWidth="1" style="67" min="4" max="4"/>
+    <col width="35" customWidth="1" style="67" min="5" max="5"/>
+    <col width="30" customWidth="1" style="67" min="6" max="6"/>
+    <col width="40" customWidth="1" style="67" min="7" max="7"/>
+    <col width="12" customWidth="1" style="67" min="8" max="8"/>
+    <col width="35" customWidth="1" style="67" min="9" max="9"/>
+    <col width="14" customWidth="1" style="67" min="10" max="10"/>
+    <col width="12" customWidth="1" style="67" min="11" max="11"/>
+    <col width="12" customWidth="1" style="67" min="12" max="12"/>
+    <col width="15" customWidth="1" style="67" min="13" max="13"/>
+    <col width="30" customWidth="1" style="67" min="14" max="14"/>
+    <col width="40" customWidth="1" style="67" min="15" max="15"/>
+    <col width="10" customWidth="1" style="67" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Name: </t>
+        </is>
+      </c>
+      <c r="B1" s="68" t="inlineStr">
+        <is>
+          <t>Visdum 2.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="67">
+      <c r="A2" s="69" t="inlineStr">
+        <is>
+          <t>Jira ID</t>
+        </is>
+      </c>
+      <c r="B2" s="69" t="inlineStr">
+        <is>
+          <t>Test Scenario ID</t>
+        </is>
+      </c>
+      <c r="C2" s="69" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D2" s="69" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="E2" s="69" t="inlineStr">
+        <is>
+          <t>Test Case Description</t>
+        </is>
+      </c>
+      <c r="F2" s="69" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="G2" s="69" t="inlineStr">
+        <is>
+          <t>Expected result</t>
+        </is>
+      </c>
+      <c r="H2" s="69" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+      <c r="I2" s="69" t="inlineStr">
+        <is>
+          <t>Actual result</t>
+        </is>
+      </c>
+      <c r="J2" s="69" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="K2" s="69" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="L2" s="69" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="M2" s="69" t="inlineStr">
+        <is>
+          <t>Comments/Issues</t>
+        </is>
+      </c>
+      <c r="N2" s="69" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="O2" s="69" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="P2" s="69" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="55" customHeight="1" s="67">
+      <c r="A3" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B3" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-01</t>
+        </is>
+      </c>
+      <c r="C3" s="71" t="inlineStr">
+        <is>
+          <t>Resource Creation, Edit, Delete CRUD (AC-20 to AC-24)</t>
+        </is>
+      </c>
+      <c r="D3" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-01</t>
+        </is>
+      </c>
+      <c r="E3" s="71" t="inlineStr">
+        <is>
+          <t>Verify creating a resource with Department only (Roles and Users empty)</t>
+        </is>
+      </c>
+      <c r="F3" s="71" t="inlineStr">
+        <is>
+          <t>Name: HR_Policy_2026
+Role: (Empty)
+Department: OptionsAbc
+Users: (Empty)
+File: sample.pdf</t>
+        </is>
+      </c>
+      <c r="G3" s="71" t="inlineStr">
+        <is>
+          <t>Modal closes, success toast "Resource added successfully !" is displayed. Resource appears in grid with Role empty and Department displayed.</t>
+        </is>
+      </c>
+      <c r="H3" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I3" s="71" t="inlineStr">
+        <is>
+          <t>Resource created successfully with Department only.</t>
+        </is>
+      </c>
+      <c r="J3" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K3" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L3" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M3" s="71" t="n"/>
+      <c r="N3" s="71" t="inlineStr">
+        <is>
+          <t>User is logged in as Admin and navigated to Settings &gt; Resource.</t>
+        </is>
+      </c>
+      <c r="O3" s="71" t="inlineStr">
+        <is>
+          <t>1. Navigate to Settings &gt; Resource.
+2. Click + Resource.
+3. Enter valid Resource Name.
+4. Leave Select Roles completely empty.
+5. Select a department from Select Departments.
+6. Upload a valid PDF file.
+7. Click Add.</t>
+        </is>
+      </c>
+      <c r="P3" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55" customHeight="1" s="67">
+      <c r="A4" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B4" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-01</t>
+        </is>
+      </c>
+      <c r="C4" s="71" t="inlineStr">
+        <is>
+          <t>Resource Creation, Edit, Delete CRUD (AC-20 to AC-24)</t>
+        </is>
+      </c>
+      <c r="D4" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-02</t>
+        </is>
+      </c>
+      <c r="E4" s="71" t="inlineStr">
+        <is>
+          <t>Verify creating a resource with User only (Roles and Departments empty)</t>
+        </is>
+      </c>
+      <c r="F4" s="71" t="inlineStr">
+        <is>
+          <t>Name: Onboarding_Walkthrough
+Role: (Empty)
+Department: (Empty)
+Users: John
+File: walkthrough.mp4</t>
+        </is>
+      </c>
+      <c r="G4" s="71" t="inlineStr">
+        <is>
+          <t>Modal closes, success toast "Resource added successfully !" is displayed. Resource appears in grid with Role empty, Department empty, and assigned user.</t>
+        </is>
+      </c>
+      <c r="H4" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I4" s="71" t="inlineStr">
+        <is>
+          <t>Resource created successfully with Users only.</t>
+        </is>
+      </c>
+      <c r="J4" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K4" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L4" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M4" s="71" t="n"/>
+      <c r="N4" s="71" t="inlineStr">
+        <is>
+          <t>User is logged in as Admin and navigated to Settings &gt; Resource.</t>
+        </is>
+      </c>
+      <c r="O4" s="71" t="inlineStr">
+        <is>
+          <t>1. Navigate to Settings &gt; Resource.
+2. Click + Resource.
+3. Enter valid Resource Name.
+4. Leave Select Roles and Select Departments empty.
+5. Select a user from Select Users.
+6. Upload a valid MP4 file.
+7. Click Add.</t>
+        </is>
+      </c>
+      <c r="P4" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1" s="67">
+      <c r="A5" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B5" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-01</t>
+        </is>
+      </c>
+      <c r="C5" s="71" t="inlineStr">
+        <is>
+          <t>Resource Creation, Edit, Delete CRUD (AC-20 to AC-24)</t>
+        </is>
+      </c>
+      <c r="D5" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-03</t>
+        </is>
+      </c>
+      <c r="E5" s="71" t="inlineStr">
+        <is>
+          <t>Verify creating a resource with Department and User combination without Roles</t>
+        </is>
+      </c>
+      <c r="F5" s="71" t="inlineStr">
+        <is>
+          <t>Name: Finance_Report_Q1
+Role: (Empty)
+Department: OptionsAbc
+Users: Arun, John
+File: sample.pdf</t>
+        </is>
+      </c>
+      <c r="G5" s="71" t="inlineStr">
+        <is>
+          <t>Resource saves successfully without requiring any Role. Grid reflects Department and User assignments.</t>
+        </is>
+      </c>
+      <c r="H5" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I5" s="71" t="inlineStr">
+        <is>
+          <t>Resource saved with Dept + User combo without Role.</t>
+        </is>
+      </c>
+      <c r="J5" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K5" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L5" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M5" s="71" t="n"/>
+      <c r="N5" s="71" t="inlineStr">
+        <is>
+          <t>User is logged in as Admin and navigated to Settings &gt; Resource.</t>
+        </is>
+      </c>
+      <c r="O5" s="71" t="inlineStr">
+        <is>
+          <t>1. Click + Resource.
+2. Enter Resource Name.
+3. Select Department.
+4. Select Users.
+5. Leave Roles completely empty.
+6. Upload file and submit.</t>
+        </is>
+      </c>
+      <c r="P5" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1" s="67">
+      <c r="A6" s="70" t="inlineStr">
+        <is>
+          <t>AC-21</t>
+        </is>
+      </c>
+      <c r="B6" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-01</t>
+        </is>
+      </c>
+      <c r="C6" s="71" t="inlineStr">
+        <is>
+          <t>Resource Creation, Edit, Delete CRUD (AC-20 to AC-24)</t>
+        </is>
+      </c>
+      <c r="D6" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-04</t>
+        </is>
+      </c>
+      <c r="E6" s="71" t="inlineStr">
+        <is>
+          <t>Verify editing a resource to remove all Roles while keeping Department</t>
+        </is>
+      </c>
+      <c r="F6" s="71" t="inlineStr">
+        <is>
+          <t>Target: Resource abc
+Remove: Manager, IC, Leader
+Add: Dept OptionsAbc</t>
+        </is>
+      </c>
+      <c r="G6" s="71" t="inlineStr">
+        <is>
+          <t>Resource updates successfully. Toast "Resource updated" appears. Resource now has no roles and displays the newly assigned department.</t>
+        </is>
+      </c>
+      <c r="H6" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I6" s="71" t="inlineStr">
+        <is>
+          <t>Role successfully removed while preserving department.</t>
+        </is>
+      </c>
+      <c r="J6" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K6" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L6" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M6" s="71" t="n"/>
+      <c r="N6" s="71" t="inlineStr">
+        <is>
+          <t>An existing resource with assigned roles exists in the system.</t>
+        </is>
+      </c>
+      <c r="O6" s="71" t="inlineStr">
+        <is>
+          <t>1. In Resource Table, locate an existing resource having a Role assigned (e.g., ID 24 abc).
+2. Click 3-dots action menu &gt; Edit.
+3. Verify modal title is Update Resource.
+4. Remove all selected Roles.
+5. Select at least one Department or User.
+6. Click Update.</t>
+        </is>
+      </c>
+      <c r="P6" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="55" customHeight="1" s="67">
+      <c r="A7" s="70" t="inlineStr">
+        <is>
+          <t>AC-21</t>
+        </is>
+      </c>
+      <c r="B7" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-01</t>
+        </is>
+      </c>
+      <c r="C7" s="71" t="inlineStr">
+        <is>
+          <t>Resource Creation, Edit, Delete CRUD (AC-20 to AC-24)</t>
+        </is>
+      </c>
+      <c r="D7" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-05</t>
+        </is>
+      </c>
+      <c r="E7" s="71" t="inlineStr">
+        <is>
+          <t>Verify updating a resource without Role assignment</t>
+        </is>
+      </c>
+      <c r="F7" s="71" t="inlineStr">
+        <is>
+          <t>Target: Existing resource
+Roles: Cleared
+Department: OptionsAbc</t>
+        </is>
+      </c>
+      <c r="G7" s="71" t="inlineStr">
+        <is>
+          <t>Update succeeds without validation errors because Roles is optional as long as Dept or Users has a value.</t>
+        </is>
+      </c>
+      <c r="H7" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I7" s="71" t="inlineStr">
+        <is>
+          <t>Resource updated without Role.</t>
+        </is>
+      </c>
+      <c r="J7" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K7" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L7" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M7" s="71" t="n"/>
+      <c r="N7" s="71" t="inlineStr">
+        <is>
+          <t>An existing resource exists in the system.</t>
+        </is>
+      </c>
+      <c r="O7" s="71" t="inlineStr">
+        <is>
+          <t>1. Open an existing resource in Edit mode that currently has no Roles.
+2. Modify Name or Department/Users.
+3. Keep Roles empty.
+4. Click Update.</t>
+        </is>
+      </c>
+      <c r="P7" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="55" customHeight="1" s="67">
+      <c r="A8" s="70" t="inlineStr">
+        <is>
+          <t>AC-22</t>
+        </is>
+      </c>
+      <c r="B8" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-01</t>
+        </is>
+      </c>
+      <c r="C8" s="71" t="inlineStr">
+        <is>
+          <t>Resource Creation, Edit, Delete CRUD (AC-20 to AC-24)</t>
+        </is>
+      </c>
+      <c r="D8" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-06</t>
+        </is>
+      </c>
+      <c r="E8" s="71" t="inlineStr">
+        <is>
+          <t>Verify creating a resource with Role only (backward compatibility)</t>
+        </is>
+      </c>
+      <c r="F8" s="71" t="inlineStr">
+        <is>
+          <t>Name: Manager_Handbook
+Role: Manager
+Department: (Empty)
+Users: (Empty)
+File: sample.pdf</t>
+        </is>
+      </c>
+      <c r="G8" s="71" t="inlineStr">
+        <is>
+          <t>Existing behavior preserved: resource is created successfully with Role only.</t>
+        </is>
+      </c>
+      <c r="H8" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I8" s="71" t="inlineStr">
+        <is>
+          <t>Resource created with Role only.</t>
+        </is>
+      </c>
+      <c r="J8" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K8" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L8" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M8" s="71" t="n"/>
+      <c r="N8" s="71" t="inlineStr">
+        <is>
+          <t>User is logged in as Admin and navigated to Settings &gt; Resource.</t>
+        </is>
+      </c>
+      <c r="O8" s="71" t="inlineStr">
+        <is>
+          <t>1. Click + Resource.
+2. Enter Resource Name.
+3. Select Role: Manager.
+4. Leave Department and Users empty.
+5. Upload file and click Add.</t>
+        </is>
+      </c>
+      <c r="P8" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1" s="67">
+      <c r="A9" s="70" t="inlineStr">
+        <is>
+          <t>AC-23</t>
+        </is>
+      </c>
+      <c r="B9" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-01</t>
+        </is>
+      </c>
+      <c r="C9" s="71" t="inlineStr">
+        <is>
+          <t>Resource Creation, Edit, Delete CRUD (AC-20 to AC-24)</t>
+        </is>
+      </c>
+      <c r="D9" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-07</t>
+        </is>
+      </c>
+      <c r="E9" s="71" t="inlineStr">
+        <is>
+          <t>Verify creating a resource with Role, Department, and User combined</t>
+        </is>
+      </c>
+      <c r="F9" s="71" t="inlineStr">
+        <is>
+          <t>Name: Comp_Plan_Overview
+Roles: Manager, Leader
+Dept: OptionsAbc
+Users: Arun, John
+File: sample.pdf</t>
+        </is>
+      </c>
+      <c r="G9" s="71" t="inlineStr">
+        <is>
+          <t>Existing multi-assignment behavior preserved: resource is created with all 3 assignment types properly linked.</t>
+        </is>
+      </c>
+      <c r="H9" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I9" s="71" t="inlineStr">
+        <is>
+          <t>Resource created with Role + Dept + Users.</t>
+        </is>
+      </c>
+      <c r="J9" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K9" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L9" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M9" s="71" t="n"/>
+      <c r="N9" s="71" t="inlineStr">
+        <is>
+          <t>User is logged in as Admin and navigated to Settings &gt; Resource.</t>
+        </is>
+      </c>
+      <c r="O9" s="71" t="inlineStr">
+        <is>
+          <t>1. Click + Resource.
+2. Enter Resource Name.
+3. Select multiple Roles.
+4. Select multiple Departments.
+5. Select multiple Users.
+6. Upload file and click Add.</t>
+        </is>
+      </c>
+      <c r="P9" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1" s="67">
+      <c r="A10" s="70" t="inlineStr">
+        <is>
+          <t>AC-24</t>
+        </is>
+      </c>
+      <c r="B10" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-01</t>
+        </is>
+      </c>
+      <c r="C10" s="71" t="inlineStr">
+        <is>
+          <t>Resource Creation, Edit, Delete CRUD (AC-20 to AC-24)</t>
+        </is>
+      </c>
+      <c r="D10" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-08</t>
+        </is>
+      </c>
+      <c r="E10" s="71" t="inlineStr">
+        <is>
+          <t>Verify validation error when creating a resource with no assignment (no Role, Dept, or User)</t>
+        </is>
+      </c>
+      <c r="F10" s="71" t="inlineStr">
+        <is>
+          <t>Name: Unassigned_Resource
+Roles: (None)
+Department: (None)
+Users: (None)
+File: sample.pdf</t>
+        </is>
+      </c>
+      <c r="G10" s="71" t="inlineStr">
+        <is>
+          <t>System blocks form submission. Red validation alert displays: "Please assign the resource to at least one role, department, or user.". No API call is made.</t>
+        </is>
+      </c>
+      <c r="H10" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I10" s="71" t="inlineStr">
+        <is>
+          <t>Submission blocked, error message displayed.</t>
+        </is>
+      </c>
+      <c r="J10" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K10" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L10" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M10" s="71" t="n"/>
+      <c r="N10" s="71" t="inlineStr">
+        <is>
+          <t>User is on Settings &gt; Resource Add Modal.</t>
+        </is>
+      </c>
+      <c r="O10" s="71" t="inlineStr">
+        <is>
+          <t>1. Click + Resource.
+2. Enter valid Resource Name.
+3. Upload valid file.
+4. Leave Select Roles, Select Departments, AND Select Users all completely empty.
+5. Click Add.</t>
+        </is>
+      </c>
+      <c r="P10" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="55" customHeight="1" s="67">
+      <c r="A11" s="70" t="inlineStr">
+        <is>
+          <t>AC-24</t>
+        </is>
+      </c>
+      <c r="B11" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-01</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="inlineStr">
+        <is>
+          <t>Resource Creation, Edit, Delete CRUD (AC-20 to AC-24)</t>
+        </is>
+      </c>
+      <c r="D11" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-09</t>
+        </is>
+      </c>
+      <c r="E11" s="71" t="inlineStr">
+        <is>
+          <t>Verify validation error when editing a resource and clearing all assignments</t>
+        </is>
+      </c>
+      <c r="F11" s="71" t="inlineStr">
+        <is>
+          <t>Target: Existing resource
+Roles: Cleared
+Department: Cleared
+Users: Cleared</t>
+        </is>
+      </c>
+      <c r="G11" s="71" t="inlineStr">
+        <is>
+          <t>Update blocked. Error "Please assign the resource to at least one role, department, or user." displays.</t>
+        </is>
+      </c>
+      <c r="H11" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I11" s="71" t="inlineStr">
+        <is>
+          <t>Update blocked, error displayed.</t>
+        </is>
+      </c>
+      <c r="J11" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K11" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L11" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M11" s="71" t="n"/>
+      <c r="N11" s="71" t="inlineStr">
+        <is>
+          <t>An existing resource is opened in Edit mode.</t>
+        </is>
+      </c>
+      <c r="O11" s="71" t="inlineStr">
+        <is>
+          <t>1. Open existing resource in Edit mode.
+2. Clear all Roles.
+3. Clear all Departments.
+4. Clear all Users.
+5. Click Update.</t>
+        </is>
+      </c>
+      <c r="P11" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="55" customHeight="1" s="67">
+      <c r="A12" s="70" t="inlineStr">
+        <is>
+          <t>AC-24</t>
+        </is>
+      </c>
+      <c r="B12" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-01</t>
+        </is>
+      </c>
+      <c r="C12" s="71" t="inlineStr">
+        <is>
+          <t>Resource Creation, Edit, Delete CRUD (AC-20 to AC-24)</t>
+        </is>
+      </c>
+      <c r="D12" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-10</t>
+        </is>
+      </c>
+      <c r="E12" s="71" t="inlineStr">
+        <is>
+          <t>Verify assignment validation error dynamically clears upon selecting a Department or User</t>
+        </is>
+      </c>
+      <c r="F12" s="71" t="inlineStr">
+        <is>
+          <t>Department: Tech</t>
+        </is>
+      </c>
+      <c r="G12" s="71" t="inlineStr">
+        <is>
+          <t>Error message dynamically clears the moment any Department, Role, or User is selected, and reappears when all selections are cleared.</t>
+        </is>
+      </c>
+      <c r="H12" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I12" s="71" t="inlineStr">
+        <is>
+          <t>Error clears on selection and reappears on removal.</t>
+        </is>
+      </c>
+      <c r="J12" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K12" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L12" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M12" s="71" t="n"/>
+      <c r="N12" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open with validation error displayed.</t>
+        </is>
+      </c>
+      <c r="O12" s="71" t="inlineStr">
+        <is>
+          <t>1. In Add Resource modal, leave all 3 assignment fields empty and click Add to trigger error.
+2. Now select a Department (or User or Role).
+3. Deselect it again.</t>
+        </is>
+      </c>
+      <c r="P12" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1" s="67">
+      <c r="A13" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B13" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C13" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D13" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-11</t>
+        </is>
+      </c>
+      <c r="E13" s="71" t="inlineStr">
+        <is>
+          <t>Verify 'Select All' functionality in Roles multi-select dropdown</t>
+        </is>
+      </c>
+      <c r="F13" s="71" t="inlineStr">
+        <is>
+          <t>Dropdown: Select roles</t>
+        </is>
+      </c>
+      <c r="G13" s="71" t="inlineStr">
+        <is>
+          <t>All roles (Manager, Individual Contributor, Leader) are selected on first click; all are deselected on second click.</t>
+        </is>
+      </c>
+      <c r="H13" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I13" s="71" t="inlineStr">
+        <is>
+          <t>Multi-select "Select All" works as expected.</t>
+        </is>
+      </c>
+      <c r="J13" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K13" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L13" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M13" s="71" t="n"/>
+      <c r="N13" s="71" t="inlineStr">
+        <is>
+          <t>Add or Edit Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O13" s="71" t="inlineStr">
+        <is>
+          <t>1. Open Roles dropdown.
+2. Click Select All checkbox.
+3. Click Select All again.</t>
+        </is>
+      </c>
+      <c r="P13" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1" s="67">
+      <c r="A14" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B14" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C14" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D14" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-12</t>
+        </is>
+      </c>
+      <c r="E14" s="71" t="inlineStr">
+        <is>
+          <t>Verify 'Select All' functionality in Departments multi-select dropdown</t>
+        </is>
+      </c>
+      <c r="F14" s="71" t="inlineStr">
+        <is>
+          <t>Dropdown: Select departments</t>
+        </is>
+      </c>
+      <c r="G14" s="71" t="inlineStr">
+        <is>
+          <t>All departments in the organization are selected on first click; all are deselected on second click.</t>
+        </is>
+      </c>
+      <c r="H14" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I14" s="71" t="inlineStr">
+        <is>
+          <t>Departments "Select All" functions correctly.</t>
+        </is>
+      </c>
+      <c r="J14" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K14" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L14" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M14" s="71" t="n"/>
+      <c r="N14" s="71" t="inlineStr">
+        <is>
+          <t>Add or Edit Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O14" s="71" t="inlineStr">
+        <is>
+          <t>1. Open Add Resource modal.
+2. Click Select Departments dropdown.
+3. Click Select All.
+4. Click Select All again.</t>
+        </is>
+      </c>
+      <c r="P14" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1" s="67">
+      <c r="A15" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B15" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C15" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D15" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-13</t>
+        </is>
+      </c>
+      <c r="E15" s="71" t="inlineStr">
+        <is>
+          <t>Verify 'Select All' functionality in Users multi-select dropdown</t>
+        </is>
+      </c>
+      <c r="F15" s="71" t="inlineStr">
+        <is>
+          <t>Dropdown: Select users</t>
+        </is>
+      </c>
+      <c r="G15" s="71" t="inlineStr">
+        <is>
+          <t>All organization users are selected on first click; all are deselected on second click.</t>
+        </is>
+      </c>
+      <c r="H15" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I15" s="71" t="inlineStr">
+        <is>
+          <t>Users "Select All" functions correctly.</t>
+        </is>
+      </c>
+      <c r="J15" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K15" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L15" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M15" s="71" t="n"/>
+      <c r="N15" s="71" t="inlineStr">
+        <is>
+          <t>Add or Edit Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O15" s="71" t="inlineStr">
+        <is>
+          <t>1. Open Add Resource modal.
+2. Click Select Users dropdown.
+3. Click Select All.
+4. Click Select All again.</t>
+        </is>
+      </c>
+      <c r="P15" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="55" customHeight="1" s="67">
+      <c r="A16" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B16" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C16" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D16" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-14</t>
+        </is>
+      </c>
+      <c r="E16" s="71" t="inlineStr">
+        <is>
+          <t>Verify searching and filtering within multi-select dropdowns</t>
+        </is>
+      </c>
+      <c r="F16" s="71" t="inlineStr">
+        <is>
+          <t>Search: Options</t>
+        </is>
+      </c>
+      <c r="G16" s="71" t="inlineStr">
+        <is>
+          <t>Dropdown list filters in real-time to show only matching items (OptionsAbc).</t>
+        </is>
+      </c>
+      <c r="H16" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I16" s="71" t="inlineStr">
+        <is>
+          <t>Dropdown search filtering works accurately.</t>
+        </is>
+      </c>
+      <c r="J16" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K16" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L16" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M16" s="71" t="n"/>
+      <c r="N16" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O16" s="71" t="inlineStr">
+        <is>
+          <t>1. Open Add Resource modal.
+2. Click Select Departments.
+3. Type search keyword in search input.
+4. Verify filtered list.</t>
+        </is>
+      </c>
+      <c r="P16" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="55" customHeight="1" s="67">
+      <c r="A17" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B17" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C17" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D17" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-15</t>
+        </is>
+      </c>
+      <c r="E17" s="71" t="inlineStr">
+        <is>
+          <t>Verify mandatory Resource Name validation error when left empty</t>
+        </is>
+      </c>
+      <c r="F17" s="71" t="inlineStr">
+        <is>
+          <t>Name: (Empty)</t>
+        </is>
+      </c>
+      <c r="G17" s="71" t="inlineStr">
+        <is>
+          <t>Form is blocked. Yup validation error "Resource Name is required" displays below Name field.</t>
+        </is>
+      </c>
+      <c r="H17" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I17" s="71" t="inlineStr">
+        <is>
+          <t>Name required validation triggered.</t>
+        </is>
+      </c>
+      <c r="J17" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K17" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L17" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M17" s="71" t="n"/>
+      <c r="N17" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O17" s="71" t="inlineStr">
+        <is>
+          <t>1. Open Add Resource modal.
+2. Leave Resource Name field empty.
+3. Select Role: Manager.
+4. Upload valid file.
+5. Click Add.</t>
+        </is>
+      </c>
+      <c r="P17" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="55" customHeight="1" s="67">
+      <c r="A18" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B18" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C18" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D18" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-16</t>
+        </is>
+      </c>
+      <c r="E18" s="71" t="inlineStr">
+        <is>
+          <t>Verify maximum character limit validation for Resource Name (max 50 chars)</t>
+        </is>
+      </c>
+      <c r="F18" s="71" t="inlineStr">
+        <is>
+          <t>Name: AAAAA... (51 chars)</t>
+        </is>
+      </c>
+      <c r="G18" s="71" t="inlineStr">
+        <is>
+          <t>Yup validation error: "Resource Name must not exceed 50 characters" is displayed. Submission blocked.</t>
+        </is>
+      </c>
+      <c r="H18" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I18" s="71" t="inlineStr">
+        <is>
+          <t>Max length validation triggered.</t>
+        </is>
+      </c>
+      <c r="J18" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K18" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L18" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M18" s="71" t="n"/>
+      <c r="N18" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O18" s="71" t="inlineStr">
+        <is>
+          <t>1. Open Add Resource modal.
+2. Enter 51 characters in Resource Name field.
+3. Click Add.</t>
+        </is>
+      </c>
+      <c r="P18" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="55" customHeight="1" s="67">
+      <c r="A19" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B19" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C19" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D19" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-17</t>
+        </is>
+      </c>
+      <c r="E19" s="71" t="inlineStr">
+        <is>
+          <t>Verify Resource Name handles leading and trailing whitespaces cleanly</t>
+        </is>
+      </c>
+      <c r="F19" s="71" t="inlineStr">
+        <is>
+          <t>Name: "  Policy Document  "</t>
+        </is>
+      </c>
+      <c r="G19" s="71" t="inlineStr">
+        <is>
+          <t>Resource Name is trimmed and saved cleanly as "Policy Document".</t>
+        </is>
+      </c>
+      <c r="H19" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I19" s="71" t="inlineStr">
+        <is>
+          <t>Name trimmed properly.</t>
+        </is>
+      </c>
+      <c r="J19" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K19" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L19" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M19" s="71" t="n"/>
+      <c r="N19" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O19" s="71" t="inlineStr">
+        <is>
+          <t>1. Enter Resource Name with leading and trailing whitespaces.
+2. Submit form.</t>
+        </is>
+      </c>
+      <c r="P19" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="55" customHeight="1" s="67">
+      <c r="A20" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B20" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C20" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D20" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-18</t>
+        </is>
+      </c>
+      <c r="E20" s="71" t="inlineStr">
+        <is>
+          <t>Verify mandatory file upload validation when adding a resource</t>
+        </is>
+      </c>
+      <c r="F20" s="71" t="inlineStr">
+        <is>
+          <t>File: (None)</t>
+        </is>
+      </c>
+      <c r="G20" s="71" t="inlineStr">
+        <is>
+          <t>Form submission blocked. Error "Please upload a resource file" displays below Dropzone.</t>
+        </is>
+      </c>
+      <c r="H20" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I20" s="71" t="inlineStr">
+        <is>
+          <t>File required validation triggered.</t>
+        </is>
+      </c>
+      <c r="J20" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K20" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L20" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M20" s="71" t="n"/>
+      <c r="N20" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O20" s="71" t="inlineStr">
+        <is>
+          <t>1. Click + Resource.
+2. Fill Name: Test Resource.
+3. Select Role: Manager.
+4. Leave file unuploaded (no file in Dropzone).
+5. Click Add.</t>
+        </is>
+      </c>
+      <c r="P20" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="55" customHeight="1" s="67">
+      <c r="A21" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B21" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C21" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D21" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-19</t>
+        </is>
+      </c>
+      <c r="E21" s="71" t="inlineStr">
+        <is>
+          <t>Verify file upload is optional when updating an existing resource</t>
+        </is>
+      </c>
+      <c r="F21" s="71" t="inlineStr">
+        <is>
+          <t>Target: Resource abc
+File: Kept existing</t>
+        </is>
+      </c>
+      <c r="G21" s="71" t="inlineStr">
+        <is>
+          <t>Form validates successfully. Existing file is preserved. No "Please upload a resource file" error.</t>
+        </is>
+      </c>
+      <c r="H21" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I21" s="71" t="inlineStr">
+        <is>
+          <t>File optional on update.</t>
+        </is>
+      </c>
+      <c r="J21" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K21" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L21" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M21" s="71" t="n"/>
+      <c r="N21" s="71" t="inlineStr">
+        <is>
+          <t>An existing resource is opened in Edit mode.</t>
+        </is>
+      </c>
+      <c r="O21" s="71" t="inlineStr">
+        <is>
+          <t>1. Edit an existing resource (e.g. abc).
+2. Keep the existing uploaded file card untouched.
+3. Modify Name or Department.
+4. Click Update.</t>
+        </is>
+      </c>
+      <c r="P21" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="55" customHeight="1" s="67">
+      <c r="A22" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B22" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C22" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D22" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-20</t>
+        </is>
+      </c>
+      <c r="E22" s="71" t="inlineStr">
+        <is>
+          <t>Verify replacing existing uploaded file with a new file in edit mode</t>
+        </is>
+      </c>
+      <c r="F22" s="71" t="inlineStr">
+        <is>
+          <t>New File: new_sample.pdf</t>
+        </is>
+      </c>
+      <c r="G22" s="71" t="inlineStr">
+        <is>
+          <t>New file replaces the old one. Resource updates with new file_path and resource_type.</t>
+        </is>
+      </c>
+      <c r="H22" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I22" s="71" t="inlineStr">
+        <is>
+          <t>File replacement works smoothly.</t>
+        </is>
+      </c>
+      <c r="J22" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K22" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L22" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M22" s="71" t="n"/>
+      <c r="N22" s="71" t="inlineStr">
+        <is>
+          <t>An existing resource is opened in Edit mode.</t>
+        </is>
+      </c>
+      <c r="O22" s="71" t="inlineStr">
+        <is>
+          <t>1. Fill Name and select Role.
+2. Delete existing file card via trash icon.
+3. Dropzone displays "Drag and Drop file or Browse".
+4. Upload new file and click Update.</t>
+        </is>
+      </c>
+      <c r="P22" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="55" customHeight="1" s="67">
+      <c r="A23" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B23" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C23" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D23" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-21</t>
+        </is>
+      </c>
+      <c r="E23" s="71" t="inlineStr">
+        <is>
+          <t>Verify file type validation rejects unsupported extensions (.exe, .zip, .png, etc.)</t>
+        </is>
+      </c>
+      <c r="F23" s="71" t="inlineStr">
+        <is>
+          <t>File: malware.exe or notes.txt</t>
+        </is>
+      </c>
+      <c r="G23" s="71" t="inlineStr">
+        <is>
+          <t>Dropzone rejects the file. Error "Invalid file format. Only PDF and MP4 files are allowed." is displayed.</t>
+        </is>
+      </c>
+      <c r="H23" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I23" s="71" t="inlineStr">
+        <is>
+          <t>Invalid file type rejected.</t>
+        </is>
+      </c>
+      <c r="J23" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K23" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L23" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M23" s="71" t="n"/>
+      <c r="N23" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O23" s="71" t="inlineStr">
+        <is>
+          <t>1. In Dropzone, browse and upload an invalid file type (.exe, .zip, .png, .txt).
+2. Observe Dropzone / validation.</t>
+        </is>
+      </c>
+      <c r="P23" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="55" customHeight="1" s="67">
+      <c r="A24" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B24" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C24" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D24" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-22</t>
+        </is>
+      </c>
+      <c r="E24" s="71" t="inlineStr">
+        <is>
+          <t>Verify file size validation enforces 50 MB maximum limit</t>
+        </is>
+      </c>
+      <c r="F24" s="71" t="inlineStr">
+        <is>
+          <t>File: large_video_55mb.mp4</t>
+        </is>
+      </c>
+      <c r="G24" s="71" t="inlineStr">
+        <is>
+          <t>Yup schema validation error displayed: "Maximum file size allowed is 50 MB.". Form submission blocked.</t>
+        </is>
+      </c>
+      <c r="H24" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I24" s="71" t="inlineStr">
+        <is>
+          <t>50 MB limit enforced.</t>
+        </is>
+      </c>
+      <c r="J24" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K24" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L24" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M24" s="71" t="n"/>
+      <c r="N24" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O24" s="71" t="inlineStr">
+        <is>
+          <t>1. In Dropzone, browse and upload a file exceeding 50 MB (e.g. 52 MB PDF or MP4).</t>
+        </is>
+      </c>
+      <c r="P24" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="55" customHeight="1" s="67">
+      <c r="A25" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B25" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C25" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D25" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-23</t>
+        </is>
+      </c>
+      <c r="E25" s="71" t="inlineStr">
+        <is>
+          <t>Verify uploaded PDF file card renders correct extension icon and size</t>
+        </is>
+      </c>
+      <c r="F25" s="71" t="inlineStr">
+        <is>
+          <t>File: policy.pdf (1.2 MB)</t>
+        </is>
+      </c>
+      <c r="G25" s="71" t="inlineStr">
+        <is>
+          <t>Upload preview card renders correctly. Extension icon displays in red (fa-file-pdf).</t>
+        </is>
+      </c>
+      <c r="H25" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I25" s="71" t="inlineStr">
+        <is>
+          <t>File card details rendered accurately.</t>
+        </is>
+      </c>
+      <c r="J25" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K25" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L25" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M25" s="71" t="n"/>
+      <c r="N25" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O25" s="71" t="inlineStr">
+        <is>
+          <t>1. Upload a valid PDF file (&lt; 50 MB).
+2. Verify uploaded file card appears with PDF icon, truncated file name, file size in KB/MB, and delete icon.</t>
+        </is>
+      </c>
+      <c r="P25" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="55" customHeight="1" s="67">
+      <c r="A26" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B26" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C26" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D26" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-24</t>
+        </is>
+      </c>
+      <c r="E26" s="71" t="inlineStr">
+        <is>
+          <t>Verify uploaded MP4 file card renders video icon and correct size</t>
+        </is>
+      </c>
+      <c r="F26" s="71" t="inlineStr">
+        <is>
+          <t>File: demo.mp4 (15 MB)</t>
+        </is>
+      </c>
+      <c r="G26" s="71" t="inlineStr">
+        <is>
+          <t>Upload preview card renders with video icon and correct size. Type resolves to video.</t>
+        </is>
+      </c>
+      <c r="H26" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I26" s="71" t="inlineStr">
+        <is>
+          <t>MP4 upload accepted and typed as video.</t>
+        </is>
+      </c>
+      <c r="J26" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K26" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L26" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M26" s="71" t="n"/>
+      <c r="N26" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O26" s="71" t="inlineStr">
+        <is>
+          <t>1. Upload a valid MP4 file (&lt; 50 MB).
+2. Verify uploaded file card appears with video icon in blue (fa-file-video), file name, size, and trash icon.</t>
+        </is>
+      </c>
+      <c r="P26" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="55" customHeight="1" s="67">
+      <c r="A27" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B27" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-02</t>
+        </is>
+      </c>
+      <c r="C27" s="71" t="inlineStr">
+        <is>
+          <t>Form Field Validations &amp; Boundary Testing (AC-26)</t>
+        </is>
+      </c>
+      <c r="D27" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-25</t>
+        </is>
+      </c>
+      <c r="E27" s="71" t="inlineStr">
+        <is>
+          <t>Verify removing an uploaded file via trash icon restores file required validation</t>
+        </is>
+      </c>
+      <c r="F27" s="71" t="inlineStr">
+        <is>
+          <t>File: test.pdf -&gt; Deleted via trash icon</t>
+        </is>
+      </c>
+      <c r="G27" s="71" t="inlineStr">
+        <is>
+          <t>File card disappears. Dropzone returns to "Drag and Drop file or Browse" state. Validation "Please upload a resource file" appears if submitted.</t>
+        </is>
+      </c>
+      <c r="H27" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I27" s="71" t="inlineStr">
+        <is>
+          <t>File removal works and restores required validation.</t>
+        </is>
+      </c>
+      <c r="J27" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K27" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L27" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M27" s="71" t="n"/>
+      <c r="N27" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open with a file uploaded.</t>
+        </is>
+      </c>
+      <c r="O27" s="71" t="inlineStr">
+        <is>
+          <t>1. Upload a file.
+2. Click the trash icon on the uploaded file card.
+3. Click Add.</t>
+        </is>
+      </c>
+      <c r="P27" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="55" customHeight="1" s="67">
+      <c r="A28" s="70" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B28" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-03</t>
+        </is>
+      </c>
+      <c r="C28" s="71" t="inlineStr">
+        <is>
+          <t>Resource Visibility &amp; Access Control (AC-25)</t>
+        </is>
+      </c>
+      <c r="D28" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-26</t>
+        </is>
+      </c>
+      <c r="E28" s="71" t="inlineStr">
+        <is>
+          <t>Verify cancelling Add/Update Resource modal discards changes without API call</t>
+        </is>
+      </c>
+      <c r="F28" s="71" t="inlineStr">
+        <is>
+          <t>Form filled with data</t>
+        </is>
+      </c>
+      <c r="G28" s="71" t="inlineStr">
+        <is>
+          <t>Modal closes immediately, no API call made, and form values are reset to initial empty state.</t>
+        </is>
+      </c>
+      <c r="H28" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I28" s="71" t="inlineStr">
+        <is>
+          <t>Modal closes and state is reset.</t>
+        </is>
+      </c>
+      <c r="J28" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K28" s="70" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L28" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M28" s="71" t="n"/>
+      <c r="N28" s="71" t="inlineStr">
+        <is>
+          <t>Add Resource modal is open.</t>
+        </is>
+      </c>
+      <c r="O28" s="71" t="inlineStr">
+        <is>
+          <t>1. In Add Resource modal, enter form values.
+2. Click Cancel button.</t>
+        </is>
+      </c>
+      <c r="P28" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="55" customHeight="1" s="67">
+      <c r="A29" s="70" t="inlineStr">
+        <is>
+          <t>AC-25</t>
+        </is>
+      </c>
+      <c r="B29" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-03</t>
+        </is>
+      </c>
+      <c r="C29" s="71" t="inlineStr">
+        <is>
+          <t>Resource Visibility &amp; Access Control (AC-25)</t>
+        </is>
+      </c>
+      <c r="D29" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-27</t>
+        </is>
+      </c>
+      <c r="E29" s="71" t="inlineStr">
+        <is>
+          <t>Verify role-based access control restricts resource visibility to assigned Manager role only</t>
+        </is>
+      </c>
+      <c r="F29" s="71" t="inlineStr">
+        <is>
+          <t>Resource: Manager_Strategy
+Role: Manager</t>
+        </is>
+      </c>
+      <c r="G29" s="71" t="inlineStr">
+        <is>
+          <t>1. Manager (John) can see the resource.
+2. IC (Arun) cannot see the resource in grid or header dropdown.</t>
+        </is>
+      </c>
+      <c r="H29" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I29" s="71" t="inlineStr">
+        <is>
+          <t>Access restricted strictly to Manager role.</t>
+        </is>
+      </c>
+      <c r="J29" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K29" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L29" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M29" s="71" t="n"/>
+      <c r="N29" s="71" t="inlineStr">
+        <is>
+          <t>Users John (Manager) and Arun (IC) exist in system.</t>
+        </is>
+      </c>
+      <c r="O29" s="71" t="inlineStr">
+        <is>
+          <t>1. Admin creates resource assigned to Role: Manager only.
+2. Log in as Manager (John, ID 3638).
+3. Check Resource Table.
+4. Log in as IC (Arun, ID 3639).
+5. Check Resource Table.</t>
+        </is>
+      </c>
+      <c r="P29" s="70" t="n"/>
+    </row>
+    <row r="30" ht="55" customHeight="1" s="67">
+      <c r="A30" s="70" t="inlineStr">
+        <is>
+          <t>AC-25</t>
+        </is>
+      </c>
+      <c r="B30" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-03</t>
+        </is>
+      </c>
+      <c r="C30" s="71" t="inlineStr">
+        <is>
+          <t>Resource Visibility &amp; Access Control (AC-25)</t>
+        </is>
+      </c>
+      <c r="D30" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-28</t>
+        </is>
+      </c>
+      <c r="E30" s="71" t="inlineStr">
+        <is>
+          <t>Verify department-based access control grants visibility to all members of assigned department</t>
+        </is>
+      </c>
+      <c r="F30" s="71" t="inlineStr">
+        <is>
+          <t>Resource: Dept_Guidelines
+Department: OptionsAbc (428)
+Roles: (Empty)</t>
+        </is>
+      </c>
+      <c r="G30" s="71" t="inlineStr">
+        <is>
+          <t>Both John and Arun can access the resource because their department matches OptionsAbc, regardless of their role. User from different department cannot see it.</t>
+        </is>
+      </c>
+      <c r="H30" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I30" s="71" t="inlineStr">
+        <is>
+          <t>Department-only visibility verified across multiple roles.</t>
+        </is>
+      </c>
+      <c r="J30" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K30" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L30" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M30" s="71" t="n"/>
+      <c r="N30" s="71" t="inlineStr">
+        <is>
+          <t>Department OptionsAbc has assigned members.</t>
+        </is>
+      </c>
+      <c r="O30" s="71" t="inlineStr">
+        <is>
+          <t>1. Admin creates resource assigned to Department: OptionsAbc only (Roles empty).
+2. Log in as John (Manager in OptionsAbc).
+3. Log in as Arun (IC in OptionsAbc).
+4. Log in as User in different Dept.</t>
+        </is>
+      </c>
+      <c r="P30" s="70" t="n"/>
+    </row>
+    <row r="31" ht="55" customHeight="1" s="67">
+      <c r="A31" s="70" t="inlineStr">
+        <is>
+          <t>AC-25</t>
+        </is>
+      </c>
+      <c r="B31" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-03</t>
+        </is>
+      </c>
+      <c r="C31" s="71" t="inlineStr">
+        <is>
+          <t>Resource Visibility &amp; Access Control (AC-25)</t>
+        </is>
+      </c>
+      <c r="D31" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-29</t>
+        </is>
+      </c>
+      <c r="E31" s="71" t="inlineStr">
+        <is>
+          <t>Verify user-based access control restricts visibility strictly to assigned individual user</t>
+        </is>
+      </c>
+      <c r="F31" s="71" t="inlineStr">
+        <is>
+          <t>Resource: Arun_Specific_Plan
+Users: Arun (ID 3639)</t>
+        </is>
+      </c>
+      <c r="G31" s="71" t="inlineStr">
+        <is>
+          <t>Arun can view the resource. John cannot view the resource even though they share the same department.</t>
+        </is>
+      </c>
+      <c r="H31" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I31" s="71" t="inlineStr">
+        <is>
+          <t>Specific user visibility verified.</t>
+        </is>
+      </c>
+      <c r="J31" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K31" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L31" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M31" s="71" t="n"/>
+      <c r="N31" s="71" t="inlineStr">
+        <is>
+          <t>Arun and John exist in system.</t>
+        </is>
+      </c>
+      <c r="O31" s="71" t="inlineStr">
+        <is>
+          <t>1. Admin creates resource assigned to Users: Arun only (Roles empty, Dept empty).
+2. Log in as Arun.
+3. Log in as John (same dept, but not assigned).</t>
+        </is>
+      </c>
+      <c r="P31" s="70" t="n"/>
+    </row>
+    <row r="32" ht="55" customHeight="1" s="67">
+      <c r="A32" s="70" t="inlineStr">
+        <is>
+          <t>AC-25</t>
+        </is>
+      </c>
+      <c r="B32" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-03</t>
+        </is>
+      </c>
+      <c r="C32" s="71" t="inlineStr">
+        <is>
+          <t>Resource Visibility &amp; Access Control (AC-25)</t>
+        </is>
+      </c>
+      <c r="D32" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-30</t>
+        </is>
+      </c>
+      <c r="E32" s="71" t="inlineStr">
+        <is>
+          <t>Verify compound assignment condition (Role AND Department) is strictly enforced</t>
+        </is>
+      </c>
+      <c r="F32" s="71" t="inlineStr">
+        <is>
+          <t>Resource: Manager_Dept_Sync
+Role: Manager
+Dept: OptionsAbc</t>
+        </is>
+      </c>
+      <c r="G32" s="71" t="inlineStr">
+        <is>
+          <t>John can view the resource (satisfies both). Arun cannot view it (matches department but fails role). Manager in different dept cannot view it.</t>
+        </is>
+      </c>
+      <c r="H32" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I32" s="71" t="inlineStr">
+        <is>
+          <t>AND condition between Role &amp; Department enforced.</t>
+        </is>
+      </c>
+      <c r="J32" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K32" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L32" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M32" s="71" t="n"/>
+      <c r="N32" s="71" t="inlineStr">
+        <is>
+          <t>Users with matching/mismatching role and department exist.</t>
+        </is>
+      </c>
+      <c r="O32" s="71" t="inlineStr">
+        <is>
+          <t>1. Admin creates resource assigned to Role: Manager AND Department: OptionsAbc.
+2. Log in as John (Manager + OptionsAbc).
+3. Log in as Arun (IC + OptionsAbc).
+4. Log in as Manager in different Dept.</t>
+        </is>
+      </c>
+      <c r="P32" s="70" t="n"/>
+    </row>
+    <row r="33" ht="55" customHeight="1" s="67">
+      <c r="A33" s="70" t="inlineStr">
+        <is>
+          <t>AC-25</t>
+        </is>
+      </c>
+      <c r="B33" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-03</t>
+        </is>
+      </c>
+      <c r="C33" s="71" t="inlineStr">
+        <is>
+          <t>Resource Visibility &amp; Access Control (AC-25)</t>
+        </is>
+      </c>
+      <c r="D33" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-31</t>
+        </is>
+      </c>
+      <c r="E33" s="71" t="inlineStr">
+        <is>
+          <t>Verify Admin user has full unrestricted visibility across all organization resources</t>
+        </is>
+      </c>
+      <c r="F33" s="71" t="inlineStr">
+        <is>
+          <t>Logged in as: Mayank Saxena (Admin)</t>
+        </is>
+      </c>
+      <c r="G33" s="71" t="inlineStr">
+        <is>
+          <t>Admin sees all organization resources unrestricted by roles, departments, or users (isIndividualContributor / isManager filters bypassed in query).</t>
+        </is>
+      </c>
+      <c r="H33" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I33" s="71" t="inlineStr">
+        <is>
+          <t>Admin has full unrestricted access to all resources.</t>
+        </is>
+      </c>
+      <c r="J33" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K33" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L33" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M33" s="71" t="n"/>
+      <c r="N33" s="71" t="inlineStr">
+        <is>
+          <t>Admin user is logged in.</t>
+        </is>
+      </c>
+      <c r="O33" s="71" t="inlineStr">
+        <is>
+          <t>1. Admin logs into the application.
+2. Check Resource Table.</t>
+        </is>
+      </c>
+      <c r="P33" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="55" customHeight="1" s="67">
+      <c r="A34" s="70" t="inlineStr">
+        <is>
+          <t>AC-25</t>
+        </is>
+      </c>
+      <c r="B34" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-03</t>
+        </is>
+      </c>
+      <c r="C34" s="71" t="inlineStr">
+        <is>
+          <t>Resource Visibility &amp; Access Control (AC-25)</t>
+        </is>
+      </c>
+      <c r="D34" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-32</t>
+        </is>
+      </c>
+      <c r="E34" s="71" t="inlineStr">
+        <is>
+          <t>Verify header Resources dropdown displays accessible resources with preview action</t>
+        </is>
+      </c>
+      <c r="F34" s="71" t="inlineStr">
+        <is>
+          <t>Visible resource in dropdown</t>
+        </is>
+      </c>
+      <c r="G34" s="71" t="inlineStr">
+        <is>
+          <t>Dropdown lists accessible resources with proper icon (fa-file-pdf in red or fa-file-video in blue). Long names (&gt; 25 chars) show tooltip. Clicking "View" opens the preview modal.</t>
+        </is>
+      </c>
+      <c r="H34" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I34" s="71" t="inlineStr">
+        <is>
+          <t>Header dropdown functions seamlessly.</t>
+        </is>
+      </c>
+      <c r="J34" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K34" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L34" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M34" s="71" t="n"/>
+      <c r="N34" s="71" t="inlineStr">
+        <is>
+          <t>User is logged in and has assigned resources.</t>
+        </is>
+      </c>
+      <c r="O34" s="71" t="inlineStr">
+        <is>
+          <t>1. Log in as target user.
+2. Click Resources icon/menu in the top navigation header.
+3. Inspect the dropdown list (ResourceDropdown.tsx).
+4. Verify resource name, file type icon, and "View" action button.
+5. Click View.</t>
+        </is>
+      </c>
+      <c r="P34" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="55" customHeight="1" s="67">
+      <c r="A35" s="70" t="inlineStr">
+        <is>
+          <t>AC-25</t>
+        </is>
+      </c>
+      <c r="B35" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-03</t>
+        </is>
+      </c>
+      <c r="C35" s="71" t="inlineStr">
+        <is>
+          <t>Resource Visibility &amp; Access Control (AC-25)</t>
+        </is>
+      </c>
+      <c r="D35" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-33</t>
+        </is>
+      </c>
+      <c r="E35" s="71" t="inlineStr">
+        <is>
+          <t>Verify header Resources dropdown displays 'No resource found' empty state when unassigned</t>
+        </is>
+      </c>
+      <c r="F35" s="71" t="inlineStr">
+        <is>
+          <t>User with 0 assigned resources</t>
+        </is>
+      </c>
+      <c r="G35" s="71" t="inlineStr">
+        <is>
+          <t>Dropdown renders "No resource found" message gracefully.</t>
+        </is>
+      </c>
+      <c r="H35" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I35" s="71" t="inlineStr">
+        <is>
+          <t>Empty state handled properly.</t>
+        </is>
+      </c>
+      <c r="J35" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K35" s="70" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L35" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M35" s="71" t="n"/>
+      <c r="N35" s="71" t="inlineStr">
+        <is>
+          <t>User has zero assigned resources.</t>
+        </is>
+      </c>
+      <c r="O35" s="71" t="inlineStr">
+        <is>
+          <t>1. Log in as user who has no resources assigned.
+2. Open Resources header dropdown.</t>
+        </is>
+      </c>
+      <c r="P35" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="55" customHeight="1" s="67">
+      <c r="A36" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B36" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C36" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D36" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-34</t>
+        </is>
+      </c>
+      <c r="E36" s="71" t="inlineStr">
+        <is>
+          <t>Verify Resource AG-Grid table renders correct columns per specification</t>
+        </is>
+      </c>
+      <c r="F36" s="71" t="inlineStr">
+        <is>
+          <t>Grid table view</t>
+        </is>
+      </c>
+      <c r="G36" s="71" t="inlineStr">
+        <is>
+          <t>Columns rendered: Name, Role, Department, Resource Type, Action (pinned right).</t>
+        </is>
+      </c>
+      <c r="H36" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I36" s="71" t="inlineStr">
+        <is>
+          <t>Table structure conforms to _resourceColumnDefs.ts.</t>
+        </is>
+      </c>
+      <c r="J36" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K36" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L36" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M36" s="71" t="n"/>
+      <c r="N36" s="71" t="inlineStr">
+        <is>
+          <t>User is on Settings &gt; Resource.</t>
+        </is>
+      </c>
+      <c r="O36" s="71" t="inlineStr">
+        <is>
+          <t>1. Navigate to Settings &gt; Resource.
+2. Verify AG-Grid columns rendered.</t>
+        </is>
+      </c>
+      <c r="P36" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="55" customHeight="1" s="67">
+      <c r="A37" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B37" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C37" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D37" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-35</t>
+        </is>
+      </c>
+      <c r="E37" s="71" t="inlineStr">
+        <is>
+          <t>Verify quick search filters resource records accurately by Name</t>
+        </is>
+      </c>
+      <c r="F37" s="71" t="inlineStr">
+        <is>
+          <t>Search: abc</t>
+        </is>
+      </c>
+      <c r="G37" s="71" t="inlineStr">
+        <is>
+          <t>Grid instantly filters to rows containing "abc". Clearing search restores all rows.</t>
+        </is>
+      </c>
+      <c r="H37" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I37" s="71" t="inlineStr">
+        <is>
+          <t>Quick search by Name works smoothly.</t>
+        </is>
+      </c>
+      <c r="J37" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K37" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L37" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M37" s="71" t="n"/>
+      <c r="N37" s="71" t="inlineStr">
+        <is>
+          <t>User is on Settings &gt; Resource with populated grid.</t>
+        </is>
+      </c>
+      <c r="O37" s="71" t="inlineStr">
+        <is>
+          <t>1. Type existing resource name in quick search box (#filter-box).
+2. Check filtered rows.
+3. Clear search box.</t>
+        </is>
+      </c>
+      <c r="P37" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="55" customHeight="1" s="67">
+      <c r="A38" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B38" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C38" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D38" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-36</t>
+        </is>
+      </c>
+      <c r="E38" s="71" t="inlineStr">
+        <is>
+          <t>Verify quick search filters resource records by Resource Type (Document / MP4 File)</t>
+        </is>
+      </c>
+      <c r="F38" s="71" t="inlineStr">
+        <is>
+          <t>Search: Document, MP4 File</t>
+        </is>
+      </c>
+      <c r="G38" s="71" t="inlineStr">
+        <is>
+          <t>getQuickFilterText filters rows by formatted Resource Type ("Document" or "MP4 File").</t>
+        </is>
+      </c>
+      <c r="H38" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I38" s="71" t="inlineStr">
+        <is>
+          <t>Quick search by Resource Type works.</t>
+        </is>
+      </c>
+      <c r="J38" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K38" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L38" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M38" s="71" t="n"/>
+      <c r="N38" s="71" t="inlineStr">
+        <is>
+          <t>User is on Settings &gt; Resource with populated grid.</t>
+        </is>
+      </c>
+      <c r="O38" s="71" t="inlineStr">
+        <is>
+          <t>1. Type Document in search box.
+2. Type MP4 File in search box.</t>
+        </is>
+      </c>
+      <c r="P38" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="55" customHeight="1" s="67">
+      <c r="A39" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B39" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C39" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D39" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-37</t>
+        </is>
+      </c>
+      <c r="E39" s="71" t="inlineStr">
+        <is>
+          <t>Verify AG-Grid column menu Set Filter functions correctly on Name column</t>
+        </is>
+      </c>
+      <c r="F39" s="71" t="inlineStr">
+        <is>
+          <t>Column Set Filter on Name</t>
+        </is>
+      </c>
+      <c r="G39" s="71" t="inlineStr">
+        <is>
+          <t>Grid displays only records matching the selected filter item.</t>
+        </is>
+      </c>
+      <c r="H39" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I39" s="71" t="inlineStr">
+        <is>
+          <t>AG-Grid column filtering functions properly.</t>
+        </is>
+      </c>
+      <c r="J39" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K39" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L39" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M39" s="71" t="n"/>
+      <c r="N39" s="71" t="inlineStr">
+        <is>
+          <t>User is on Settings &gt; Resource with populated grid.</t>
+        </is>
+      </c>
+      <c r="O39" s="71" t="inlineStr">
+        <is>
+          <t>1. Click column menu on Name column.
+2. Apply Set Filter for a specific resource name.</t>
+        </is>
+      </c>
+      <c r="P39" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="55" customHeight="1" s="67">
+      <c r="A40" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B40" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C40" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D40" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-38</t>
+        </is>
+      </c>
+      <c r="E40" s="71" t="inlineStr">
+        <is>
+          <t>Verify AG-Grid column header click sorts Name column ascending and descending</t>
+        </is>
+      </c>
+      <c r="F40" s="71" t="inlineStr">
+        <is>
+          <t>Column: Name</t>
+        </is>
+      </c>
+      <c r="G40" s="71" t="inlineStr">
+        <is>
+          <t>Rows sort alphabetically ascending (A-Z) and descending (Z-A).</t>
+        </is>
+      </c>
+      <c r="H40" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I40" s="71" t="inlineStr">
+        <is>
+          <t>Column sorting works correctly.</t>
+        </is>
+      </c>
+      <c r="J40" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K40" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L40" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M40" s="71" t="n"/>
+      <c r="N40" s="71" t="inlineStr">
+        <is>
+          <t>User is on Settings &gt; Resource with populated grid.</t>
+        </is>
+      </c>
+      <c r="O40" s="71" t="inlineStr">
+        <is>
+          <t>1. Click on Name header to sort ascending.
+2. Click again to sort descending.</t>
+        </is>
+      </c>
+      <c r="P40" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="55" customHeight="1" s="67">
+      <c r="A41" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B41" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C41" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D41" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-39</t>
+        </is>
+      </c>
+      <c r="E41" s="71" t="inlineStr">
+        <is>
+          <t>Verify clicking View button opens preview modal and embeds PDF in iframe</t>
+        </is>
+      </c>
+      <c r="F41" s="71" t="inlineStr">
+        <is>
+          <t>Resource Type: document</t>
+        </is>
+      </c>
+      <c r="G41" s="71" t="inlineStr">
+        <is>
+          <t>Preview modal opens with title "Preview". Body renders an &lt;iframe&gt; displaying the PDF from S3 (file_path).</t>
+        </is>
+      </c>
+      <c r="H41" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I41" s="71" t="inlineStr">
+        <is>
+          <t>PDF rendered in preview modal.</t>
+        </is>
+      </c>
+      <c r="J41" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K41" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L41" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M41" s="71" t="n"/>
+      <c r="N41" s="71" t="inlineStr">
+        <is>
+          <t>At least one PDF resource exists in the table.</t>
+        </is>
+      </c>
+      <c r="O41" s="71" t="inlineStr">
+        <is>
+          <t>1. Locate a PDF resource row.
+2. Click inline View button in the Action cell.</t>
+        </is>
+      </c>
+      <c r="P41" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="55" customHeight="1" s="67">
+      <c r="A42" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B42" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C42" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D42" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-40</t>
+        </is>
+      </c>
+      <c r="E42" s="71" t="inlineStr">
+        <is>
+          <t>Verify clicking View button opens preview modal and plays MP4 video</t>
+        </is>
+      </c>
+      <c r="F42" s="71" t="inlineStr">
+        <is>
+          <t>Resource Type: video</t>
+        </is>
+      </c>
+      <c r="G42" s="71" t="inlineStr">
+        <is>
+          <t>Preview modal opens. &lt;ReactPlayer&gt; renders with video controls enabled (Play, Pause, Volume, Fullscreen) at 16:9 aspect ratio.</t>
+        </is>
+      </c>
+      <c r="H42" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I42" s="71" t="inlineStr">
+        <is>
+          <t>Video player renders and plays file.</t>
+        </is>
+      </c>
+      <c r="J42" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K42" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L42" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M42" s="71" t="n"/>
+      <c r="N42" s="71" t="inlineStr">
+        <is>
+          <t>At least one MP4 video resource exists in the table.</t>
+        </is>
+      </c>
+      <c r="O42" s="71" t="inlineStr">
+        <is>
+          <t>1. Locate an MP4 resource row.
+2. Click inline View button.</t>
+        </is>
+      </c>
+      <c r="P42" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="55" customHeight="1" s="67">
+      <c r="A43" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B43" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C43" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D43" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-41</t>
+        </is>
+      </c>
+      <c r="E43" s="71" t="inlineStr">
+        <is>
+          <t>Verify 3-dots action menu renders Edit and Delete options</t>
+        </is>
+      </c>
+      <c r="F43" s="71" t="inlineStr">
+        <is>
+          <t>Action Menu</t>
+        </is>
+      </c>
+      <c r="G43" s="71" t="inlineStr">
+        <is>
+          <t>Global dropdown menu opens containing Edit (warning/yellow icon) and Delete (danger/red icon).</t>
+        </is>
+      </c>
+      <c r="H43" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I43" s="71" t="inlineStr">
+        <is>
+          <t>Action menu options rendered.</t>
+        </is>
+      </c>
+      <c r="J43" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K43" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L43" s="70" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M43" s="71" t="n"/>
+      <c r="N43" s="71" t="inlineStr">
+        <is>
+          <t>User is on Settings &gt; Resource with populated grid.</t>
+        </is>
+      </c>
+      <c r="O43" s="71" t="inlineStr">
+        <is>
+          <t>1. In row Action cell, click 3-dots ellipsis icon (#userAction{id}).
+2. Verify dropdown menu options.</t>
+        </is>
+      </c>
+      <c r="P43" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="55" customHeight="1" s="67">
+      <c r="A44" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B44" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C44" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D44" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-42</t>
+        </is>
+      </c>
+      <c r="E44" s="71" t="inlineStr">
+        <is>
+          <t>Verify Edit modal pre-populates all existing resource data accurately</t>
+        </is>
+      </c>
+      <c r="F44" s="71" t="inlineStr">
+        <is>
+          <t>Resource: abc</t>
+        </is>
+      </c>
+      <c r="G44" s="71" t="inlineStr">
+        <is>
+          <t>Modal title is "Update Resource". Submit button text is "Update". Name, Roles, Departments, Users, and existing file card are pre-populated accurately.</t>
+        </is>
+      </c>
+      <c r="H44" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I44" s="71" t="inlineStr">
+        <is>
+          <t>Edit modal pre-populates all existing data.</t>
+        </is>
+      </c>
+      <c r="J44" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K44" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L44" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M44" s="71" t="n"/>
+      <c r="N44" s="71" t="inlineStr">
+        <is>
+          <t>User is on Settings &gt; Resource.</t>
+        </is>
+      </c>
+      <c r="O44" s="71" t="inlineStr">
+        <is>
+          <t>1. Click 3-dots &gt; Edit on a resource.
+2. Verify modal fields pre-populated.</t>
+        </is>
+      </c>
+      <c r="P44" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="55" customHeight="1" s="67">
+      <c r="A45" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B45" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C45" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D45" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-43</t>
+        </is>
+      </c>
+      <c r="E45" s="71" t="inlineStr">
+        <is>
+          <t>Verify Delete confirmation modal appears with Visdum warning and can be cancelled</t>
+        </is>
+      </c>
+      <c r="F45" s="71" t="inlineStr">
+        <is>
+          <t>Delete modal</t>
+        </is>
+      </c>
+      <c r="G45" s="71" t="inlineStr">
+        <is>
+          <t>Modal displays Visdum logo and "Are you sure you want to delete this resource?". Clicking Cancel closes modal without deleting.</t>
+        </is>
+      </c>
+      <c r="H45" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I45" s="71" t="inlineStr">
+        <is>
+          <t>Confirmation modal displayed and dismissible.</t>
+        </is>
+      </c>
+      <c r="J45" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K45" s="70" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L45" s="70" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M45" s="71" t="n"/>
+      <c r="N45" s="71" t="inlineStr">
+        <is>
+          <t>User is on Settings &gt; Resource.</t>
+        </is>
+      </c>
+      <c r="O45" s="71" t="inlineStr">
+        <is>
+          <t>1. Click 3-dots &gt; Delete on a resource.
+2. Verify confirmation modal.
+3. Click Cancel.</t>
+        </is>
+      </c>
+      <c r="P45" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="55" customHeight="1" s="67">
+      <c r="A46" s="70" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B46" s="70" t="inlineStr">
+        <is>
+          <t>TS-RES-04</t>
+        </is>
+      </c>
+      <c r="C46" s="71" t="inlineStr">
+        <is>
+          <t>Table Grid, Search, Sorting, Filtering &amp; Actions</t>
+        </is>
+      </c>
+      <c r="D46" s="70" t="inlineStr">
+        <is>
+          <t>TC-RES-44</t>
+        </is>
+      </c>
+      <c r="E46" s="71" t="inlineStr">
+        <is>
+          <t>Verify confirming Delete removes resource via API, shows toast, and refreshes grid</t>
+        </is>
+      </c>
+      <c r="F46" s="71" t="inlineStr">
+        <is>
+          <t>Target: Test resource</t>
+        </is>
+      </c>
+      <c r="G46" s="71" t="inlineStr">
+        <is>
+          <t>Resource deleted via DELETE /api/resource/{id}. Success toast "Resource Deleted Successfully" appears. Grid refetches and resource disappears.</t>
+        </is>
+      </c>
+      <c r="H46" s="70" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I46" s="71" t="inlineStr">
+        <is>
+          <t>Resource deleted and grid refreshed.</t>
+        </is>
+      </c>
+      <c r="J46" s="70" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="K46" s="70" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L46" s="70" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M46" s="71" t="n"/>
+      <c r="N46" s="71" t="inlineStr">
+        <is>
+          <t>User is on Settings &gt; Resource.</t>
+        </is>
+      </c>
+      <c r="O46" s="71" t="inlineStr">
+        <is>
+          <t>1. Click 3-dots &gt; Delete.
+2. Click Submit (Confirm delete).</t>
+        </is>
+      </c>
+      <c r="P46" s="70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/src/test/resources/manual-testcases-runnable.xlsx
+++ b/src/test/resources/manual-testcases-runnable.xlsx
@@ -8,6 +8,7 @@
     <sheet name="Team" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Departments" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Resources" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Refresh Columns" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="dd-mm-yyyy"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <name val="Arial"/>
       <color rgb="FF000000"/>
@@ -101,8 +102,23 @@
       <name val="Arial"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -144,8 +160,14 @@
         <bgColor rgb="00E9ECEF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border/>
     <border>
       <left style="thin">
@@ -236,11 +258,25 @@
         <color rgb="00D3D3D3"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -430,6 +466,16 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -34927,7 +34973,7 @@
       </c>
       <c r="P3" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35015,7 +35061,7 @@
       </c>
       <c r="P4" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35102,7 +35148,7 @@
       </c>
       <c r="P5" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35187,7 +35233,7 @@
       </c>
       <c r="P6" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35270,7 +35316,7 @@
       </c>
       <c r="P7" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35356,7 +35402,7 @@
       </c>
       <c r="P8" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35443,7 +35489,7 @@
       </c>
       <c r="P9" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35529,7 +35575,7 @@
       </c>
       <c r="P10" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35614,7 +35660,7 @@
       </c>
       <c r="P11" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35694,7 +35740,7 @@
       </c>
       <c r="P12" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35774,7 +35820,7 @@
       </c>
       <c r="P13" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35855,7 +35901,7 @@
       </c>
       <c r="P14" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -35936,7 +35982,7 @@
       </c>
       <c r="P15" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36017,7 +36063,7 @@
       </c>
       <c r="P16" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36099,7 +36145,7 @@
       </c>
       <c r="P17" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36179,7 +36225,7 @@
       </c>
       <c r="P18" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36258,7 +36304,7 @@
       </c>
       <c r="P19" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36340,7 +36386,7 @@
       </c>
       <c r="P20" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36422,7 +36468,7 @@
       </c>
       <c r="P21" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36503,7 +36549,7 @@
       </c>
       <c r="P22" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36582,7 +36628,7 @@
       </c>
       <c r="P23" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36660,7 +36706,7 @@
       </c>
       <c r="P24" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36739,7 +36785,7 @@
       </c>
       <c r="P25" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36818,7 +36864,7 @@
       </c>
       <c r="P26" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36898,7 +36944,7 @@
       </c>
       <c r="P27" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -36977,7 +37023,7 @@
       </c>
       <c r="P28" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -37059,7 +37105,11 @@
 5. Check Resource Table.</t>
         </is>
       </c>
-      <c r="P29" s="70" t="n"/>
+      <c r="P29" s="70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="55" customHeight="1" s="67">
       <c r="A30" s="70" t="inlineStr">
@@ -37138,7 +37188,11 @@
 4. Log in as User in different Dept.</t>
         </is>
       </c>
-      <c r="P30" s="70" t="n"/>
+      <c r="P30" s="70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="55" customHeight="1" s="67">
       <c r="A31" s="70" t="inlineStr">
@@ -37215,7 +37269,11 @@
 3. Log in as John (same dept, but not assigned).</t>
         </is>
       </c>
-      <c r="P31" s="70" t="n"/>
+      <c r="P31" s="70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="55" customHeight="1" s="67">
       <c r="A32" s="70" t="inlineStr">
@@ -37294,7 +37352,11 @@
 4. Log in as Manager in different Dept.</t>
         </is>
       </c>
-      <c r="P32" s="70" t="n"/>
+      <c r="P32" s="70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="55" customHeight="1" s="67">
       <c r="A33" s="70" t="inlineStr">
@@ -37371,7 +37433,7 @@
       </c>
       <c r="P33" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -37453,7 +37515,7 @@
       </c>
       <c r="P34" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -37532,7 +37594,7 @@
       </c>
       <c r="P35" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -37611,7 +37673,7 @@
       </c>
       <c r="P36" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -37691,7 +37753,7 @@
       </c>
       <c r="P37" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -37770,7 +37832,7 @@
       </c>
       <c r="P38" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -37849,7 +37911,7 @@
       </c>
       <c r="P39" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -37928,7 +37990,7 @@
       </c>
       <c r="P40" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38007,7 +38069,7 @@
       </c>
       <c r="P41" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38086,7 +38148,7 @@
       </c>
       <c r="P42" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38165,7 +38227,7 @@
       </c>
       <c r="P43" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38244,7 +38306,7 @@
       </c>
       <c r="P44" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38324,7 +38386,7 @@
       </c>
       <c r="P45" s="70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -38402,6 +38464,4730 @@
         </is>
       </c>
       <c r="P46" s="70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:P64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="67" min="1" max="1"/>
+    <col width="16" customWidth="1" style="67" min="2" max="2"/>
+    <col width="40" customWidth="1" style="67" min="3" max="3"/>
+    <col width="14" customWidth="1" style="67" min="4" max="4"/>
+    <col width="40" customWidth="1" style="67" min="5" max="5"/>
+    <col width="35" customWidth="1" style="67" min="6" max="6"/>
+    <col width="40" customWidth="1" style="67" min="7" max="7"/>
+    <col width="12" customWidth="1" style="67" min="8" max="8"/>
+    <col width="15" customWidth="1" style="67" min="9" max="9"/>
+    <col width="12" customWidth="1" style="67" min="10" max="10"/>
+    <col width="12" customWidth="1" style="67" min="11" max="11"/>
+    <col width="12" customWidth="1" style="67" min="12" max="12"/>
+    <col width="15" customWidth="1" style="67" min="13" max="13"/>
+    <col width="35" customWidth="1" style="67" min="14" max="14"/>
+    <col width="45" customWidth="1" style="67" min="15" max="15"/>
+    <col width="10" customWidth="1" style="67" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Project Name: </t>
+        </is>
+      </c>
+      <c r="B1" s="72" t="inlineStr">
+        <is>
+          <t>Visdum 2.0 - Raw Data: Refresh Columns</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="67">
+      <c r="A2" s="73" t="inlineStr">
+        <is>
+          <t>Jira ID</t>
+        </is>
+      </c>
+      <c r="B2" s="73" t="inlineStr">
+        <is>
+          <t>Test Scenario ID</t>
+        </is>
+      </c>
+      <c r="C2" s="73" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D2" s="73" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="E2" s="73" t="inlineStr">
+        <is>
+          <t>Test Case Description</t>
+        </is>
+      </c>
+      <c r="F2" s="73" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="G2" s="73" t="inlineStr">
+        <is>
+          <t>Expected result</t>
+        </is>
+      </c>
+      <c r="H2" s="73" t="inlineStr">
+        <is>
+          <t>Test Status</t>
+        </is>
+      </c>
+      <c r="I2" s="73" t="inlineStr">
+        <is>
+          <t>Actual result</t>
+        </is>
+      </c>
+      <c r="J2" s="73" t="inlineStr">
+        <is>
+          <t>Test Date</t>
+        </is>
+      </c>
+      <c r="K2" s="73" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="L2" s="73" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="M2" s="73" t="inlineStr">
+        <is>
+          <t>Comments/Issues</t>
+        </is>
+      </c>
+      <c r="N2" s="73" t="inlineStr">
+        <is>
+          <t>Preconditions</t>
+        </is>
+      </c>
+      <c r="O2" s="73" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="P2" s="73" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1" s="67">
+      <c r="A3" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B3" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C3" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns action is displayed for a standard Raw Data stream containing a Derived Column</t>
+        </is>
+      </c>
+      <c r="D3" s="74" t="inlineStr">
+        <is>
+          <t>TC-01</t>
+        </is>
+      </c>
+      <c r="E3" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns action is displayed for a standard Raw Data stream containing a Derived Column</t>
+        </is>
+      </c>
+      <c r="F3" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with at least 1 Derived Column</t>
+        </is>
+      </c>
+      <c r="G3" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns option is displayed.</t>
+        </is>
+      </c>
+      <c r="H3" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I3" s="75" t="inlineStr"/>
+      <c r="J3" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K3" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L3" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M3" s="75" t="inlineStr"/>
+      <c r="N3" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with at least 1 Derived Column</t>
+        </is>
+      </c>
+      <c r="O3" s="75" t="inlineStr">
+        <is>
+          <t>1. Open Raw Data.
+2. Locate the eligible Data Stream.
+3. Open the table-level Action menu.</t>
+        </is>
+      </c>
+      <c r="P3" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="67">
+      <c r="A4" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B4" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C4" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns action is displayed for a standard Raw Data stream containing a Lookup Column</t>
+        </is>
+      </c>
+      <c r="D4" s="74" t="inlineStr">
+        <is>
+          <t>TC-02</t>
+        </is>
+      </c>
+      <c r="E4" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns action is displayed for a standard Raw Data stream containing a Lookup Column</t>
+        </is>
+      </c>
+      <c r="F4" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with at least 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="G4" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns option is displayed.</t>
+        </is>
+      </c>
+      <c r="H4" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I4" s="75" t="inlineStr"/>
+      <c r="J4" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K4" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L4" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M4" s="75" t="inlineStr"/>
+      <c r="N4" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with at least 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="O4" s="75" t="inlineStr">
+        <is>
+          <t>1. Open Raw Data.
+2. Open Action menu for the stream.</t>
+        </is>
+      </c>
+      <c r="P4" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" s="67">
+      <c r="A5" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B5" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C5" s="75" t="inlineStr">
+        <is>
+          <t>Verify action is displayed when the stream contains both Derived and Lookup Columns</t>
+        </is>
+      </c>
+      <c r="D5" s="74" t="inlineStr">
+        <is>
+          <t>TC-03</t>
+        </is>
+      </c>
+      <c r="E5" s="75" t="inlineStr">
+        <is>
+          <t>Verify action is displayed when the stream contains both Derived and Lookup Columns</t>
+        </is>
+      </c>
+      <c r="F5" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream containing at least 1 Derived and 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="G5" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns is displayed only once.</t>
+        </is>
+      </c>
+      <c r="H5" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I5" s="75" t="inlineStr"/>
+      <c r="J5" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K5" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L5" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M5" s="75" t="inlineStr"/>
+      <c r="N5" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream containing at least 1 Derived and 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="O5" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P5" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="67">
+      <c r="A6" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B6" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C6" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns is hidden when the stream has no Derived/Lookup Columns</t>
+        </is>
+      </c>
+      <c r="D6" s="74" t="inlineStr">
+        <is>
+          <t>TC-04</t>
+        </is>
+      </c>
+      <c r="E6" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns is hidden when the stream has no Derived/Lookup Columns</t>
+        </is>
+      </c>
+      <c r="F6" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with only normal/raw columns</t>
+        </is>
+      </c>
+      <c r="G6" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns is not displayed.</t>
+        </is>
+      </c>
+      <c r="H6" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I6" s="75" t="inlineStr"/>
+      <c r="J6" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K6" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L6" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M6" s="75" t="inlineStr"/>
+      <c r="N6" s="75" t="inlineStr">
+        <is>
+          <t>Standard Raw Data stream with only normal/raw columns</t>
+        </is>
+      </c>
+      <c r="O6" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P6" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="67">
+      <c r="A7" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B7" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C7" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns is hidden for a Key-Value Data Stream</t>
+        </is>
+      </c>
+      <c r="D7" s="74" t="inlineStr">
+        <is>
+          <t>TC-05</t>
+        </is>
+      </c>
+      <c r="E7" s="75" t="inlineStr">
+        <is>
+          <t>Verify Refresh Columns is hidden for a Key-Value Data Stream</t>
+        </is>
+      </c>
+      <c r="F7" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value Data Stream containing eligible column configuration if supported</t>
+        </is>
+      </c>
+      <c r="G7" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns is not displayed.</t>
+        </is>
+      </c>
+      <c r="H7" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I7" s="75" t="inlineStr"/>
+      <c r="J7" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K7" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L7" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M7" s="75" t="inlineStr"/>
+      <c r="N7" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value Data Stream containing eligible column configuration if supported</t>
+        </is>
+      </c>
+      <c r="O7" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P7" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="67">
+      <c r="A8" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B8" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C8" s="75" t="inlineStr">
+        <is>
+          <t>Verify Key-Value stream is excluded even if no/other columns are present</t>
+        </is>
+      </c>
+      <c r="D8" s="74" t="inlineStr">
+        <is>
+          <t>TC-06</t>
+        </is>
+      </c>
+      <c r="E8" s="75" t="inlineStr">
+        <is>
+          <t>Verify Key-Value stream is excluded even if no/other columns are present</t>
+        </is>
+      </c>
+      <c r="F8" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value Data Stream</t>
+        </is>
+      </c>
+      <c r="G8" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns remains unavailable.</t>
+        </is>
+      </c>
+      <c r="H8" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I8" s="75" t="inlineStr"/>
+      <c r="J8" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K8" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L8" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M8" s="75" t="inlineStr"/>
+      <c r="N8" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value Data Stream</t>
+        </is>
+      </c>
+      <c r="O8" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P8" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="67">
+      <c r="A9" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B9" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C9" s="75" t="inlineStr">
+        <is>
+          <t>Verify action label is exactly correct</t>
+        </is>
+      </c>
+      <c r="D9" s="74" t="inlineStr">
+        <is>
+          <t>TC-07</t>
+        </is>
+      </c>
+      <c r="E9" s="75" t="inlineStr">
+        <is>
+          <t>Verify action label is exactly correct</t>
+        </is>
+      </c>
+      <c r="F9" s="75" t="inlineStr">
+        <is>
+          <t>Eligible standard Raw Data stream</t>
+        </is>
+      </c>
+      <c r="G9" s="75" t="inlineStr">
+        <is>
+          <t>Label appears as Refresh Columns.</t>
+        </is>
+      </c>
+      <c r="H9" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I9" s="75" t="inlineStr"/>
+      <c r="J9" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K9" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L9" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M9" s="75" t="inlineStr"/>
+      <c r="N9" s="75" t="inlineStr">
+        <is>
+          <t>Eligible standard Raw Data stream</t>
+        </is>
+      </c>
+      <c r="O9" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P9" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1" s="67">
+      <c r="A10" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B10" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C10" s="75" t="inlineStr">
+        <is>
+          <t>Verify no existing Action menu options are changed</t>
+        </is>
+      </c>
+      <c r="D10" s="74" t="inlineStr">
+        <is>
+          <t>TC-08</t>
+        </is>
+      </c>
+      <c r="E10" s="75" t="inlineStr">
+        <is>
+          <t>Verify no existing Action menu options are changed</t>
+        </is>
+      </c>
+      <c r="F10" s="75" t="inlineStr">
+        <is>
+          <t>Existing Raw Data stream</t>
+        </is>
+      </c>
+      <c r="G10" s="75" t="inlineStr">
+        <is>
+          <t>Existing actions remain unchanged in label/functionality.</t>
+        </is>
+      </c>
+      <c r="H10" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I10" s="75" t="inlineStr"/>
+      <c r="J10" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K10" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L10" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M10" s="75" t="inlineStr"/>
+      <c r="N10" s="75" t="inlineStr">
+        <is>
+          <t>Existing Raw Data stream</t>
+        </is>
+      </c>
+      <c r="O10" s="75" t="inlineStr">
+        <is>
+          <t>Open Action menu before/after feature availability.</t>
+        </is>
+      </c>
+      <c r="P10" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="67">
+      <c r="A11" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B11" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C11" s="75" t="inlineStr">
+        <is>
+          <t>Open confirmation modal by clicking Refresh Columns</t>
+        </is>
+      </c>
+      <c r="D11" s="74" t="inlineStr">
+        <is>
+          <t>TC-09</t>
+        </is>
+      </c>
+      <c r="E11" s="75" t="inlineStr">
+        <is>
+          <t>Open confirmation modal by clicking Refresh Columns</t>
+        </is>
+      </c>
+      <c r="F11" s="75" t="inlineStr">
+        <is>
+          <t>Eligible Data Stream with Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="G11" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal opens.</t>
+        </is>
+      </c>
+      <c r="H11" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I11" s="75" t="inlineStr"/>
+      <c r="J11" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K11" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L11" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M11" s="75" t="inlineStr"/>
+      <c r="N11" s="75" t="inlineStr">
+        <is>
+          <t>Eligible Data Stream with Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="O11" s="75" t="inlineStr">
+        <is>
+          <t>1. Open Action menu.
+2. Click Refresh Columns.</t>
+        </is>
+      </c>
+      <c r="P11" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="67">
+      <c r="A12" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B12" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-01</t>
+        </is>
+      </c>
+      <c r="C12" s="75" t="inlineStr">
+        <is>
+          <t>Verify confirmation message</t>
+        </is>
+      </c>
+      <c r="D12" s="74" t="inlineStr">
+        <is>
+          <t>TC-10</t>
+        </is>
+      </c>
+      <c r="E12" s="75" t="inlineStr">
+        <is>
+          <t>Verify confirmation message</t>
+        </is>
+      </c>
+      <c r="F12" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G12" s="75" t="inlineStr">
+        <is>
+          <t>Message is exactly: “Are you sure you want to refresh all Derived and Lookup Column values?”</t>
+        </is>
+      </c>
+      <c r="H12" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I12" s="75" t="inlineStr"/>
+      <c r="J12" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K12" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L12" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M12" s="75" t="inlineStr"/>
+      <c r="N12" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O12" s="75" t="inlineStr">
+        <is>
+          <t>Read modal content.</t>
+        </is>
+      </c>
+      <c r="P12" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1" s="67">
+      <c r="A13" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B13" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C13" s="75" t="inlineStr">
+        <is>
+          <t>Verify Cancel button is displayed and secondary/lighter</t>
+        </is>
+      </c>
+      <c r="D13" s="74" t="inlineStr">
+        <is>
+          <t>TC-11</t>
+        </is>
+      </c>
+      <c r="E13" s="75" t="inlineStr">
+        <is>
+          <t>Verify Cancel button is displayed and secondary/lighter</t>
+        </is>
+      </c>
+      <c r="F13" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G13" s="75" t="inlineStr">
+        <is>
+          <t>Cancel is displayed as secondary/lighter action.</t>
+        </is>
+      </c>
+      <c r="H13" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I13" s="75" t="inlineStr"/>
+      <c r="J13" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K13" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L13" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M13" s="75" t="inlineStr"/>
+      <c r="N13" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O13" s="75" t="inlineStr">
+        <is>
+          <t>Observe buttons.</t>
+        </is>
+      </c>
+      <c r="P13" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="67">
+      <c r="A14" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B14" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C14" s="75" t="inlineStr">
+        <is>
+          <t>Verify Submit button is displayed and primary/darker</t>
+        </is>
+      </c>
+      <c r="D14" s="74" t="inlineStr">
+        <is>
+          <t>TC-12</t>
+        </is>
+      </c>
+      <c r="E14" s="75" t="inlineStr">
+        <is>
+          <t>Verify Submit button is displayed and primary/darker</t>
+        </is>
+      </c>
+      <c r="F14" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G14" s="75" t="inlineStr">
+        <is>
+          <t>Submit is displayed as primary/darker action.</t>
+        </is>
+      </c>
+      <c r="H14" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I14" s="75" t="inlineStr"/>
+      <c r="J14" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K14" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L14" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M14" s="75" t="inlineStr"/>
+      <c r="N14" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O14" s="75" t="inlineStr">
+        <is>
+          <t>Observe buttons.</t>
+        </is>
+      </c>
+      <c r="P14" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="67">
+      <c r="A15" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B15" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C15" s="75" t="inlineStr">
+        <is>
+          <t>Verify Cancel closes confirmation modal without processing</t>
+        </is>
+      </c>
+      <c r="D15" s="74" t="inlineStr">
+        <is>
+          <t>TC-13</t>
+        </is>
+      </c>
+      <c r="E15" s="75" t="inlineStr">
+        <is>
+          <t>Verify Cancel closes confirmation modal without processing</t>
+        </is>
+      </c>
+      <c r="F15" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G15" s="75" t="inlineStr">
+        <is>
+          <t>Modal closes and no processing starts.</t>
+        </is>
+      </c>
+      <c r="H15" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I15" s="75" t="inlineStr"/>
+      <c r="J15" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K15" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L15" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M15" s="75" t="inlineStr"/>
+      <c r="N15" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O15" s="75" t="inlineStr">
+        <is>
+          <t>Click Cancel.</t>
+        </is>
+      </c>
+      <c r="P15" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1" s="67">
+      <c r="A16" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B16" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C16" s="75" t="inlineStr">
+        <is>
+          <t>Verify clicking outside/close icon behavior</t>
+        </is>
+      </c>
+      <c r="D16" s="74" t="inlineStr">
+        <is>
+          <t>TC-14</t>
+        </is>
+      </c>
+      <c r="E16" s="75" t="inlineStr">
+        <is>
+          <t>Verify clicking outside/close icon behavior</t>
+        </is>
+      </c>
+      <c r="F16" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G16" s="75" t="inlineStr">
+        <is>
+          <t>Modal closes according to existing modal behavior and processing does not start.</t>
+        </is>
+      </c>
+      <c r="H16" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I16" s="75" t="inlineStr"/>
+      <c r="J16" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K16" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L16" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M16" s="75" t="inlineStr"/>
+      <c r="N16" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O16" s="75" t="inlineStr">
+        <is>
+          <t>Click supported close control/outside modal if standard behavior exists.</t>
+        </is>
+      </c>
+      <c r="P16" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="67">
+      <c r="A17" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B17" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C17" s="75" t="inlineStr">
+        <is>
+          <t>Verify Submit starts bulk column refresh</t>
+        </is>
+      </c>
+      <c r="D17" s="74" t="inlineStr">
+        <is>
+          <t>TC-15</t>
+        </is>
+      </c>
+      <c r="E17" s="75" t="inlineStr">
+        <is>
+          <t>Verify Submit starts bulk column refresh</t>
+        </is>
+      </c>
+      <c r="F17" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="G17" s="75" t="inlineStr">
+        <is>
+          <t>Processing starts for all applicable columns.</t>
+        </is>
+      </c>
+      <c r="H17" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I17" s="75" t="inlineStr"/>
+      <c r="J17" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K17" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L17" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M17" s="75" t="inlineStr"/>
+      <c r="N17" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="O17" s="75" t="inlineStr">
+        <is>
+          <t>1. Open Refresh Columns.
+2. Click Submit.</t>
+        </is>
+      </c>
+      <c r="P17" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" s="67">
+      <c r="A18" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B18" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C18" s="75" t="inlineStr">
+        <is>
+          <t>Verify all Derived Columns are included in refresh</t>
+        </is>
+      </c>
+      <c r="D18" s="74" t="inlineStr">
+        <is>
+          <t>TC-16</t>
+        </is>
+      </c>
+      <c r="E18" s="75" t="inlineStr">
+        <is>
+          <t>Verify all Derived Columns are included in refresh</t>
+        </is>
+      </c>
+      <c r="F18" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Derived Columns</t>
+        </is>
+      </c>
+      <c r="G18" s="75" t="inlineStr">
+        <is>
+          <t>Every Derived Column belonging to the selected stream is processed.</t>
+        </is>
+      </c>
+      <c r="H18" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I18" s="75" t="inlineStr"/>
+      <c r="J18" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K18" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L18" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M18" s="75" t="inlineStr"/>
+      <c r="N18" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Derived Columns</t>
+        </is>
+      </c>
+      <c r="O18" s="75" t="inlineStr">
+        <is>
+          <t>Trigger Refresh Columns and monitor processing/result.</t>
+        </is>
+      </c>
+      <c r="P18" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="67">
+      <c r="A19" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B19" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C19" s="75" t="inlineStr">
+        <is>
+          <t>Verify all Lookup Columns are included in refresh</t>
+        </is>
+      </c>
+      <c r="D19" s="74" t="inlineStr">
+        <is>
+          <t>TC-17</t>
+        </is>
+      </c>
+      <c r="E19" s="75" t="inlineStr">
+        <is>
+          <t>Verify all Lookup Columns are included in refresh</t>
+        </is>
+      </c>
+      <c r="F19" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Lookup Columns</t>
+        </is>
+      </c>
+      <c r="G19" s="75" t="inlineStr">
+        <is>
+          <t>Every Lookup Column belonging to the selected stream is processed.</t>
+        </is>
+      </c>
+      <c r="H19" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I19" s="75" t="inlineStr"/>
+      <c r="J19" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K19" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L19" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M19" s="75" t="inlineStr"/>
+      <c r="N19" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains multiple Lookup Columns</t>
+        </is>
+      </c>
+      <c r="O19" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P19" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" s="67">
+      <c r="A20" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B20" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C20" s="75" t="inlineStr">
+        <is>
+          <t>Verify both Derived and Lookup Columns are processed together</t>
+        </is>
+      </c>
+      <c r="D20" s="74" t="inlineStr">
+        <is>
+          <t>TC-18</t>
+        </is>
+      </c>
+      <c r="E20" s="75" t="inlineStr">
+        <is>
+          <t>Verify both Derived and Lookup Columns are processed together</t>
+        </is>
+      </c>
+      <c r="F20" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 3 Derived + 2 Lookup columns</t>
+        </is>
+      </c>
+      <c r="G20" s="75" t="inlineStr">
+        <is>
+          <t>All 5 eligible columns are processed.</t>
+        </is>
+      </c>
+      <c r="H20" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I20" s="75" t="inlineStr"/>
+      <c r="J20" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K20" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L20" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M20" s="75" t="inlineStr"/>
+      <c r="N20" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 3 Derived + 2 Lookup columns</t>
+        </is>
+      </c>
+      <c r="O20" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P20" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1" s="67">
+      <c r="A21" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B21" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C21" s="75" t="inlineStr">
+        <is>
+          <t>Verify normal/raw columns are not treated as Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="D21" s="74" t="inlineStr">
+        <is>
+          <t>TC-19</t>
+        </is>
+      </c>
+      <c r="E21" s="75" t="inlineStr">
+        <is>
+          <t>Verify normal/raw columns are not treated as Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="F21" s="75" t="inlineStr">
+        <is>
+          <t>Stream has raw + Derived + Lookup columns</t>
+        </is>
+      </c>
+      <c r="G21" s="75" t="inlineStr">
+        <is>
+          <t>Raw columns are not included in Derived/Lookup processing count.</t>
+        </is>
+      </c>
+      <c r="H21" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I21" s="75" t="inlineStr"/>
+      <c r="J21" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K21" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L21" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M21" s="75" t="inlineStr"/>
+      <c r="N21" s="75" t="inlineStr">
+        <is>
+          <t>Stream has raw + Derived + Lookup columns</t>
+        </is>
+      </c>
+      <c r="O21" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P21" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="67">
+      <c r="A22" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B22" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-02</t>
+        </is>
+      </c>
+      <c r="C22" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh is scoped to selected Data Stream</t>
+        </is>
+      </c>
+      <c r="D22" s="74" t="inlineStr">
+        <is>
+          <t>TC-20</t>
+        </is>
+      </c>
+      <c r="E22" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh is scoped to selected Data Stream</t>
+        </is>
+      </c>
+      <c r="F22" s="75" t="inlineStr">
+        <is>
+          <t>Data Stream A and B both have Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="G22" s="75" t="inlineStr">
+        <is>
+          <t>Only A is processed. B remains unaffected.</t>
+        </is>
+      </c>
+      <c r="H22" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I22" s="75" t="inlineStr"/>
+      <c r="J22" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K22" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L22" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M22" s="75" t="inlineStr"/>
+      <c r="N22" s="75" t="inlineStr">
+        <is>
+          <t>Data Stream A and B both have Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="O22" s="75" t="inlineStr">
+        <is>
+          <t>1. Trigger refresh from A.
+2. Check processing/activity/data for B.</t>
+        </is>
+      </c>
+      <c r="P22" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="67">
+      <c r="A23" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B23" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C23" s="75" t="inlineStr">
+        <is>
+          <t>Verify unrelated Data Stream is not synchronized</t>
+        </is>
+      </c>
+      <c r="D23" s="74" t="inlineStr">
+        <is>
+          <t>TC-21</t>
+        </is>
+      </c>
+      <c r="E23" s="75" t="inlineStr">
+        <is>
+          <t>Verify unrelated Data Stream is not synchronized</t>
+        </is>
+      </c>
+      <c r="F23" s="75" t="inlineStr">
+        <is>
+          <t>Two independent Data Streams exist</t>
+        </is>
+      </c>
+      <c r="G23" s="75" t="inlineStr">
+        <is>
+          <t>No fetch/upload/sync is triggered for Data Stream B.</t>
+        </is>
+      </c>
+      <c r="H23" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I23" s="75" t="inlineStr"/>
+      <c r="J23" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K23" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L23" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M23" s="75" t="inlineStr"/>
+      <c r="N23" s="75" t="inlineStr">
+        <is>
+          <t>Two independent Data Streams exist</t>
+        </is>
+      </c>
+      <c r="O23" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh on Data Stream A.</t>
+        </is>
+      </c>
+      <c r="P23" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="67">
+      <c r="A24" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B24" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C24" s="75" t="inlineStr">
+        <is>
+          <t>Verify processing is asynchronous</t>
+        </is>
+      </c>
+      <c r="D24" s="74" t="inlineStr">
+        <is>
+          <t>TC-22</t>
+        </is>
+      </c>
+      <c r="E24" s="75" t="inlineStr">
+        <is>
+          <t>Verify processing is asynchronous</t>
+        </is>
+      </c>
+      <c r="F24" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream with sufficient records</t>
+        </is>
+      </c>
+      <c r="G24" s="75" t="inlineStr">
+        <is>
+          <t>User receives processing state/modal and UI is not forced to wait for synchronous completion.</t>
+        </is>
+      </c>
+      <c r="H24" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I24" s="75" t="inlineStr"/>
+      <c r="J24" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K24" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L24" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M24" s="75" t="inlineStr"/>
+      <c r="N24" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream with sufficient records</t>
+        </is>
+      </c>
+      <c r="O24" s="75" t="inlineStr">
+        <is>
+          <t>Click Submit.</t>
+        </is>
+      </c>
+      <c r="P24" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1" s="67">
+      <c r="A25" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B25" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C25" s="75" t="inlineStr">
+        <is>
+          <t>Verify standard processing modal is displayed</t>
+        </is>
+      </c>
+      <c r="D25" s="74" t="inlineStr">
+        <is>
+          <t>TC-23</t>
+        </is>
+      </c>
+      <c r="E25" s="75" t="inlineStr">
+        <is>
+          <t>Verify standard processing modal is displayed</t>
+        </is>
+      </c>
+      <c r="F25" s="75" t="inlineStr">
+        <is>
+          <t>Submit refresh request</t>
+        </is>
+      </c>
+      <c r="G25" s="75" t="inlineStr">
+        <is>
+          <t>Same processing modal/experience used by existing Derived/Lookup processing is displayed.</t>
+        </is>
+      </c>
+      <c r="H25" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I25" s="75" t="inlineStr"/>
+      <c r="J25" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K25" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L25" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M25" s="75" t="inlineStr"/>
+      <c r="N25" s="75" t="inlineStr">
+        <is>
+          <t>Submit refresh request</t>
+        </is>
+      </c>
+      <c r="O25" s="75" t="inlineStr">
+        <is>
+          <t>Click Submit.</t>
+        </is>
+      </c>
+      <c r="P25" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1" s="67">
+      <c r="A26" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B26" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C26" s="75" t="inlineStr">
+        <is>
+          <t>Verify processing modal shows running state</t>
+        </is>
+      </c>
+      <c r="D26" s="74" t="inlineStr">
+        <is>
+          <t>TC-24</t>
+        </is>
+      </c>
+      <c r="E26" s="75" t="inlineStr">
+        <is>
+          <t>Verify processing modal shows running state</t>
+        </is>
+      </c>
+      <c r="F26" s="75" t="inlineStr">
+        <is>
+          <t>Processing in progress</t>
+        </is>
+      </c>
+      <c r="G26" s="75" t="inlineStr">
+        <is>
+          <t>Modal indicates processing is in progress using existing experience.</t>
+        </is>
+      </c>
+      <c r="H26" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I26" s="75" t="inlineStr"/>
+      <c r="J26" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K26" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L26" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M26" s="75" t="inlineStr"/>
+      <c r="N26" s="75" t="inlineStr">
+        <is>
+          <t>Processing in progress</t>
+        </is>
+      </c>
+      <c r="O26" s="75" t="inlineStr">
+        <is>
+          <t>Observe processing modal.</t>
+        </is>
+      </c>
+      <c r="P26" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1" s="67">
+      <c r="A27" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B27" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C27" s="75" t="inlineStr">
+        <is>
+          <t>Verify user can leave processing modal without stopping job</t>
+        </is>
+      </c>
+      <c r="D27" s="74" t="inlineStr">
+        <is>
+          <t>TC-25</t>
+        </is>
+      </c>
+      <c r="E27" s="75" t="inlineStr">
+        <is>
+          <t>Verify user can leave processing modal without stopping job</t>
+        </is>
+      </c>
+      <c r="F27" s="75" t="inlineStr">
+        <is>
+          <t>Processing has started</t>
+        </is>
+      </c>
+      <c r="G27" s="75" t="inlineStr">
+        <is>
+          <t>Processing continues asynchronously in background.</t>
+        </is>
+      </c>
+      <c r="H27" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I27" s="75" t="inlineStr"/>
+      <c r="J27" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K27" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L27" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M27" s="75" t="inlineStr"/>
+      <c r="N27" s="75" t="inlineStr">
+        <is>
+          <t>Processing has started</t>
+        </is>
+      </c>
+      <c r="O27" s="75" t="inlineStr">
+        <is>
+          <t>Navigate away/close modal using supported behavior.</t>
+        </is>
+      </c>
+      <c r="P27" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1" s="67">
+      <c r="A28" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B28" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C28" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh continues after closing processing modal</t>
+        </is>
+      </c>
+      <c r="D28" s="74" t="inlineStr">
+        <is>
+          <t>TC-26</t>
+        </is>
+      </c>
+      <c r="E28" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh continues after closing processing modal</t>
+        </is>
+      </c>
+      <c r="F28" s="75" t="inlineStr">
+        <is>
+          <t>Processing is active</t>
+        </is>
+      </c>
+      <c r="G28" s="75" t="inlineStr">
+        <is>
+          <t>Backend processing completes successfully even though modal is no longer open.</t>
+        </is>
+      </c>
+      <c r="H28" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I28" s="75" t="inlineStr"/>
+      <c r="J28" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K28" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L28" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M28" s="75" t="inlineStr"/>
+      <c r="N28" s="75" t="inlineStr">
+        <is>
+          <t>Processing is active</t>
+        </is>
+      </c>
+      <c r="O28" s="75" t="inlineStr">
+        <is>
+          <t>Close/minimize processing experience, then wait for processing completion.</t>
+        </is>
+      </c>
+      <c r="P28" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1" s="67">
+      <c r="A29" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B29" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C29" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion modal appears when user remains on processing modal</t>
+        </is>
+      </c>
+      <c r="D29" s="74" t="inlineStr">
+        <is>
+          <t>TC-27</t>
+        </is>
+      </c>
+      <c r="E29" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion modal appears when user remains on processing modal</t>
+        </is>
+      </c>
+      <c r="F29" s="75" t="inlineStr">
+        <is>
+          <t>User remains on processing modal until completion</t>
+        </is>
+      </c>
+      <c r="G29" s="75" t="inlineStr">
+        <is>
+          <t>Processing state changes to completion modal/state.</t>
+        </is>
+      </c>
+      <c r="H29" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I29" s="75" t="inlineStr"/>
+      <c r="J29" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K29" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L29" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M29" s="75" t="inlineStr"/>
+      <c r="N29" s="75" t="inlineStr">
+        <is>
+          <t>User remains on processing modal until completion</t>
+        </is>
+      </c>
+      <c r="O29" s="75" t="inlineStr">
+        <is>
+          <t>Wait for processing to finish.</t>
+        </is>
+      </c>
+      <c r="P29" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1" s="67">
+      <c r="A30" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B30" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C30" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Columns processed count</t>
+        </is>
+      </c>
+      <c r="D30" s="74" t="inlineStr">
+        <is>
+          <t>TC-28</t>
+        </is>
+      </c>
+      <c r="E30" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Columns processed count</t>
+        </is>
+      </c>
+      <c r="F30" s="75" t="inlineStr">
+        <is>
+          <t>Example: 3 Derived Columns</t>
+        </is>
+      </c>
+      <c r="G30" s="75" t="inlineStr">
+        <is>
+          <t>Completion modal displays Derived Columns Processed: 3.</t>
+        </is>
+      </c>
+      <c r="H30" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I30" s="75" t="inlineStr"/>
+      <c r="J30" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K30" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L30" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M30" s="75" t="inlineStr"/>
+      <c r="N30" s="75" t="inlineStr">
+        <is>
+          <t>Example: 3 Derived Columns</t>
+        </is>
+      </c>
+      <c r="O30" s="75" t="inlineStr">
+        <is>
+          <t>Complete refresh.</t>
+        </is>
+      </c>
+      <c r="P30" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1" s="67">
+      <c r="A31" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B31" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C31" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup Columns processed count</t>
+        </is>
+      </c>
+      <c r="D31" s="74" t="inlineStr">
+        <is>
+          <t>TC-29</t>
+        </is>
+      </c>
+      <c r="E31" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup Columns processed count</t>
+        </is>
+      </c>
+      <c r="F31" s="75" t="inlineStr">
+        <is>
+          <t>Example: 2 Lookup Columns</t>
+        </is>
+      </c>
+      <c r="G31" s="75" t="inlineStr">
+        <is>
+          <t>Completion modal displays Lookup Columns Processed: 2.</t>
+        </is>
+      </c>
+      <c r="H31" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I31" s="75" t="inlineStr"/>
+      <c r="J31" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K31" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L31" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M31" s="75" t="inlineStr"/>
+      <c r="N31" s="75" t="inlineStr">
+        <is>
+          <t>Example: 2 Lookup Columns</t>
+        </is>
+      </c>
+      <c r="O31" s="75" t="inlineStr">
+        <is>
+          <t>Complete refresh.</t>
+        </is>
+      </c>
+      <c r="P31" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1" s="67">
+      <c r="A32" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B32" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-03</t>
+        </is>
+      </c>
+      <c r="C32" s="75" t="inlineStr">
+        <is>
+          <t>Verify Records Processed count</t>
+        </is>
+      </c>
+      <c r="D32" s="74" t="inlineStr">
+        <is>
+          <t>TC-30</t>
+        </is>
+      </c>
+      <c r="E32" s="75" t="inlineStr">
+        <is>
+          <t>Verify Records Processed count</t>
+        </is>
+      </c>
+      <c r="F32" s="75" t="inlineStr">
+        <is>
+          <t>Known dataset, e.g. 10,240 records</t>
+        </is>
+      </c>
+      <c r="G32" s="75" t="inlineStr">
+        <is>
+          <t>Count matches actual number of records processed.</t>
+        </is>
+      </c>
+      <c r="H32" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I32" s="75" t="inlineStr"/>
+      <c r="J32" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K32" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L32" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M32" s="75" t="inlineStr"/>
+      <c r="N32" s="75" t="inlineStr">
+        <is>
+          <t>Known dataset, e.g. 10,240 records</t>
+        </is>
+      </c>
+      <c r="O32" s="75" t="inlineStr">
+        <is>
+          <t>Complete refresh.</t>
+        </is>
+      </c>
+      <c r="P32" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1" s="67">
+      <c r="A33" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B33" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C33" s="75" t="inlineStr">
+        <is>
+          <t>Verify Records Updated count</t>
+        </is>
+      </c>
+      <c r="D33" s="74" t="inlineStr">
+        <is>
+          <t>TC-31</t>
+        </is>
+      </c>
+      <c r="E33" s="75" t="inlineStr">
+        <is>
+          <t>Verify Records Updated count</t>
+        </is>
+      </c>
+      <c r="F33" s="75" t="inlineStr">
+        <is>
+          <t>Dataset where known records change after refresh</t>
+        </is>
+      </c>
+      <c r="G33" s="75" t="inlineStr">
+        <is>
+          <t>Count matches actual records whose values were updated.</t>
+        </is>
+      </c>
+      <c r="H33" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I33" s="75" t="inlineStr"/>
+      <c r="J33" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K33" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L33" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M33" s="75" t="inlineStr"/>
+      <c r="N33" s="75" t="inlineStr">
+        <is>
+          <t>Dataset where known records change after refresh</t>
+        </is>
+      </c>
+      <c r="O33" s="75" t="inlineStr">
+        <is>
+          <t>Complete refresh.</t>
+        </is>
+      </c>
+      <c r="P33" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="67">
+      <c r="A34" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B34" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C34" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts when no values change</t>
+        </is>
+      </c>
+      <c r="D34" s="74" t="inlineStr">
+        <is>
+          <t>TC-32</t>
+        </is>
+      </c>
+      <c r="E34" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts when no values change</t>
+        </is>
+      </c>
+      <c r="F34" s="75" t="inlineStr">
+        <is>
+          <t>Source values already match calculated/lookup values</t>
+        </is>
+      </c>
+      <c r="G34" s="75" t="inlineStr">
+        <is>
+          <t>Records Processed reflects processed records and Records Updated reflects 0 where applicable.</t>
+        </is>
+      </c>
+      <c r="H34" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I34" s="75" t="inlineStr"/>
+      <c r="J34" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K34" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L34" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M34" s="75" t="inlineStr"/>
+      <c r="N34" s="75" t="inlineStr">
+        <is>
+          <t>Source values already match calculated/lookup values</t>
+        </is>
+      </c>
+      <c r="O34" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P34" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1" s="67">
+      <c r="A35" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B35" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C35" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts when all records change</t>
+        </is>
+      </c>
+      <c r="D35" s="74" t="inlineStr">
+        <is>
+          <t>TC-33</t>
+        </is>
+      </c>
+      <c r="E35" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts when all records change</t>
+        </is>
+      </c>
+      <c r="F35" s="75" t="inlineStr">
+        <is>
+          <t>Modify source values so all applicable values change</t>
+        </is>
+      </c>
+      <c r="G35" s="75" t="inlineStr">
+        <is>
+          <t>Records Updated reflects actual updated records.</t>
+        </is>
+      </c>
+      <c r="H35" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I35" s="75" t="inlineStr"/>
+      <c r="J35" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K35" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L35" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M35" s="75" t="inlineStr"/>
+      <c r="N35" s="75" t="inlineStr">
+        <is>
+          <t>Modify source values so all applicable values change</t>
+        </is>
+      </c>
+      <c r="O35" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P35" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1" s="67">
+      <c r="A36" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B36" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C36" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts for mixed updated/non-updated records</t>
+        </is>
+      </c>
+      <c r="D36" s="74" t="inlineStr">
+        <is>
+          <t>TC-34</t>
+        </is>
+      </c>
+      <c r="E36" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion counts for mixed updated/non-updated records</t>
+        </is>
+      </c>
+      <c r="F36" s="75" t="inlineStr">
+        <is>
+          <t>Dataset with some changed and some unchanged records</t>
+        </is>
+      </c>
+      <c r="G36" s="75" t="inlineStr">
+        <is>
+          <t>Updated count includes only actually updated records.</t>
+        </is>
+      </c>
+      <c r="H36" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I36" s="75" t="inlineStr"/>
+      <c r="J36" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K36" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L36" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M36" s="75" t="inlineStr"/>
+      <c r="N36" s="75" t="inlineStr">
+        <is>
+          <t>Dataset with some changed and some unchanged records</t>
+        </is>
+      </c>
+      <c r="O36" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P36" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1" s="67">
+      <c r="A37" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B37" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C37" s="75" t="inlineStr">
+        <is>
+          <t>Verify async locking blocks conflicting process</t>
+        </is>
+      </c>
+      <c r="D37" s="74" t="inlineStr">
+        <is>
+          <t>TC-35</t>
+        </is>
+      </c>
+      <c r="E37" s="75" t="inlineStr">
+        <is>
+          <t>Verify async locking blocks conflicting process</t>
+        </is>
+      </c>
+      <c r="F37" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns processing is running</t>
+        </is>
+      </c>
+      <c r="G37" s="75" t="inlineStr">
+        <is>
+          <t>Conflicting process is blocked according to existing async locking behavior.</t>
+        </is>
+      </c>
+      <c r="H37" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I37" s="75" t="inlineStr"/>
+      <c r="J37" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K37" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L37" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M37" s="75" t="inlineStr"/>
+      <c r="N37" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns processing is running</t>
+        </is>
+      </c>
+      <c r="O37" s="75" t="inlineStr">
+        <is>
+          <t>Attempt another conflicting async process.</t>
+        </is>
+      </c>
+      <c r="P37" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1" s="67">
+      <c r="A38" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B38" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C38" s="75" t="inlineStr">
+        <is>
+          <t>Verify another conflicting process cannot bypass lock from another UI action</t>
+        </is>
+      </c>
+      <c r="D38" s="74" t="inlineStr">
+        <is>
+          <t>TC-36</t>
+        </is>
+      </c>
+      <c r="E38" s="75" t="inlineStr">
+        <is>
+          <t>Verify another conflicting process cannot bypass lock from another UI action</t>
+        </is>
+      </c>
+      <c r="F38" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is in progress</t>
+        </is>
+      </c>
+      <c r="G38" s="75" t="inlineStr">
+        <is>
+          <t>Operation is blocked by existing async-process lock.</t>
+        </is>
+      </c>
+      <c r="H38" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I38" s="75" t="inlineStr"/>
+      <c r="J38" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K38" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L38" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M38" s="75" t="inlineStr"/>
+      <c r="N38" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is in progress</t>
+        </is>
+      </c>
+      <c r="O38" s="75" t="inlineStr">
+        <is>
+          <t>Attempt supported conflicting operation from another page/action.</t>
+        </is>
+      </c>
+      <c r="P38" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1" s="67">
+      <c r="A39" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B39" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C39" s="75" t="inlineStr">
+        <is>
+          <t>Verify non-conflicting operations follow existing locking behavior</t>
+        </is>
+      </c>
+      <c r="D39" s="74" t="inlineStr">
+        <is>
+          <t>TC-37</t>
+        </is>
+      </c>
+      <c r="E39" s="75" t="inlineStr">
+        <is>
+          <t>Verify non-conflicting operations follow existing locking behavior</t>
+        </is>
+      </c>
+      <c r="F39" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is running</t>
+        </is>
+      </c>
+      <c r="G39" s="75" t="inlineStr">
+        <is>
+          <t>Behavior follows existing async processing rules; no unexpected blocking.</t>
+        </is>
+      </c>
+      <c r="H39" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I39" s="75" t="inlineStr"/>
+      <c r="J39" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K39" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L39" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M39" s="75" t="inlineStr"/>
+      <c r="N39" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is running</t>
+        </is>
+      </c>
+      <c r="O39" s="75" t="inlineStr">
+        <is>
+          <t>Attempt unrelated/non-conflicting operation.</t>
+        </is>
+      </c>
+      <c r="P39" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1" s="67">
+      <c r="A40" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B40" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C40" s="75" t="inlineStr">
+        <is>
+          <t>Verify only one refresh can be initiated for the same stream while processing</t>
+        </is>
+      </c>
+      <c r="D40" s="74" t="inlineStr">
+        <is>
+          <t>TC-38</t>
+        </is>
+      </c>
+      <c r="E40" s="75" t="inlineStr">
+        <is>
+          <t>Verify only one refresh can be initiated for the same stream while processing</t>
+        </is>
+      </c>
+      <c r="F40" s="75" t="inlineStr">
+        <is>
+          <t>Refresh already running</t>
+        </is>
+      </c>
+      <c r="G40" s="75" t="inlineStr">
+        <is>
+          <t>Second conflicting refresh is prevented according to locking behavior.</t>
+        </is>
+      </c>
+      <c r="H40" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I40" s="75" t="inlineStr"/>
+      <c r="J40" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K40" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L40" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M40" s="75" t="inlineStr"/>
+      <c r="N40" s="75" t="inlineStr">
+        <is>
+          <t>Refresh already running</t>
+        </is>
+      </c>
+      <c r="O40" s="75" t="inlineStr">
+        <is>
+          <t>Attempt Refresh Columns again.</t>
+        </is>
+      </c>
+      <c r="P40" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1" s="67">
+      <c r="A41" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B41" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C41" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Column calculation logic is unchanged</t>
+        </is>
+      </c>
+      <c r="D41" s="74" t="inlineStr">
+        <is>
+          <t>TC-39</t>
+        </is>
+      </c>
+      <c r="E41" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Column calculation logic is unchanged</t>
+        </is>
+      </c>
+      <c r="F41" s="75" t="inlineStr">
+        <is>
+          <t>Existing Derived Column test data</t>
+        </is>
+      </c>
+      <c r="G41" s="75" t="inlineStr">
+        <is>
+          <t>Calculated values remain correct and unchanged.</t>
+        </is>
+      </c>
+      <c r="H41" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I41" s="75" t="inlineStr"/>
+      <c r="J41" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K41" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L41" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M41" s="75" t="inlineStr"/>
+      <c r="N41" s="75" t="inlineStr">
+        <is>
+          <t>Existing Derived Column test data</t>
+        </is>
+      </c>
+      <c r="O41" s="75" t="inlineStr">
+        <is>
+          <t>Run normal Derived Column calculation and compare with pre-feature behavior.</t>
+        </is>
+      </c>
+      <c r="P41" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1" s="67">
+      <c r="A42" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B42" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-04</t>
+        </is>
+      </c>
+      <c r="C42" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup Column resolution logic is unchanged</t>
+        </is>
+      </c>
+      <c r="D42" s="74" t="inlineStr">
+        <is>
+          <t>TC-40</t>
+        </is>
+      </c>
+      <c r="E42" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup Column resolution logic is unchanged</t>
+        </is>
+      </c>
+      <c r="F42" s="75" t="inlineStr">
+        <is>
+          <t>Existing Lookup setup with known mappings</t>
+        </is>
+      </c>
+      <c r="G42" s="75" t="inlineStr">
+        <is>
+          <t>Lookup values resolve exactly according to existing logic.</t>
+        </is>
+      </c>
+      <c r="H42" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I42" s="75" t="inlineStr"/>
+      <c r="J42" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K42" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L42" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M42" s="75" t="inlineStr"/>
+      <c r="N42" s="75" t="inlineStr">
+        <is>
+          <t>Existing Lookup setup with known mappings</t>
+        </is>
+      </c>
+      <c r="O42" s="75" t="inlineStr">
+        <is>
+          <t>Run refresh and compare values.</t>
+        </is>
+      </c>
+      <c r="P42" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1" s="67">
+      <c r="A43" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B43" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C43" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Column dependencies still work</t>
+        </is>
+      </c>
+      <c r="D43" s="74" t="inlineStr">
+        <is>
+          <t>TC-41</t>
+        </is>
+      </c>
+      <c r="E43" s="75" t="inlineStr">
+        <is>
+          <t>Verify Derived Column dependencies still work</t>
+        </is>
+      </c>
+      <c r="F43" s="75" t="inlineStr">
+        <is>
+          <t>Derived Column A depends on another field/column</t>
+        </is>
+      </c>
+      <c r="G43" s="75" t="inlineStr">
+        <is>
+          <t>Dependent Derived Column recalculates correctly using existing dependency logic.</t>
+        </is>
+      </c>
+      <c r="H43" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I43" s="75" t="inlineStr"/>
+      <c r="J43" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K43" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L43" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M43" s="75" t="inlineStr"/>
+      <c r="N43" s="75" t="inlineStr">
+        <is>
+          <t>Derived Column A depends on another field/column</t>
+        </is>
+      </c>
+      <c r="O43" s="75" t="inlineStr">
+        <is>
+          <t>Change source value and run refresh.</t>
+        </is>
+      </c>
+      <c r="P43" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1" s="67">
+      <c r="A44" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B44" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C44" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup dependency/source behavior remains unchanged</t>
+        </is>
+      </c>
+      <c r="D44" s="74" t="inlineStr">
+        <is>
+          <t>TC-42</t>
+        </is>
+      </c>
+      <c r="E44" s="75" t="inlineStr">
+        <is>
+          <t>Verify Lookup dependency/source behavior remains unchanged</t>
+        </is>
+      </c>
+      <c r="F44" s="75" t="inlineStr">
+        <is>
+          <t>Valid lookup source data</t>
+        </is>
+      </c>
+      <c r="G44" s="75" t="inlineStr">
+        <is>
+          <t>Lookup column gets expected value according to existing logic.</t>
+        </is>
+      </c>
+      <c r="H44" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I44" s="75" t="inlineStr"/>
+      <c r="J44" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K44" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L44" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M44" s="75" t="inlineStr"/>
+      <c r="N44" s="75" t="inlineStr">
+        <is>
+          <t>Valid lookup source data</t>
+        </is>
+      </c>
+      <c r="O44" s="75" t="inlineStr">
+        <is>
+          <t>Modify source/lookup value and refresh.</t>
+        </is>
+      </c>
+      <c r="P44" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1" s="67">
+      <c r="A45" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B45" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C45" s="75" t="inlineStr">
+        <is>
+          <t>Verify manually refreshing does not trigger full Data Stream re-fetch</t>
+        </is>
+      </c>
+      <c r="D45" s="74" t="inlineStr">
+        <is>
+          <t>TC-43</t>
+        </is>
+      </c>
+      <c r="E45" s="75" t="inlineStr">
+        <is>
+          <t>Verify manually refreshing does not trigger full Data Stream re-fetch</t>
+        </is>
+      </c>
+      <c r="F45" s="75" t="inlineStr">
+        <is>
+          <t>Existing stream with external/source data</t>
+        </is>
+      </c>
+      <c r="G45" s="75" t="inlineStr">
+        <is>
+          <t>No complete re-fetch/upload/sync is initiated.</t>
+        </is>
+      </c>
+      <c r="H45" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I45" s="75" t="inlineStr"/>
+      <c r="J45" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K45" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L45" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M45" s="75" t="inlineStr"/>
+      <c r="N45" s="75" t="inlineStr">
+        <is>
+          <t>Existing stream with external/source data</t>
+        </is>
+      </c>
+      <c r="O45" s="75" t="inlineStr">
+        <is>
+          <t>Trigger Refresh Columns.</t>
+        </is>
+      </c>
+      <c r="P45" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1" s="67">
+      <c r="A46" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B46" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C46" s="75" t="inlineStr">
+        <is>
+          <t>Verify manually refreshing does not modify raw/source records unnecessarily</t>
+        </is>
+      </c>
+      <c r="D46" s="74" t="inlineStr">
+        <is>
+          <t>TC-44</t>
+        </is>
+      </c>
+      <c r="E46" s="75" t="inlineStr">
+        <is>
+          <t>Verify manually refreshing does not modify raw/source records unnecessarily</t>
+        </is>
+      </c>
+      <c r="F46" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains raw and calculated fields</t>
+        </is>
+      </c>
+      <c r="G46" s="75" t="inlineStr">
+        <is>
+          <t>Only applicable Derived/Lookup values are recalculated/updated.</t>
+        </is>
+      </c>
+      <c r="H46" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I46" s="75" t="inlineStr"/>
+      <c r="J46" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K46" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L46" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M46" s="75" t="inlineStr"/>
+      <c r="N46" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains raw and calculated fields</t>
+        </is>
+      </c>
+      <c r="O46" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P46" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1" s="67">
+      <c r="A47" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B47" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C47" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Derived Column create flow still works</t>
+        </is>
+      </c>
+      <c r="D47" s="74" t="inlineStr">
+        <is>
+          <t>TC-45</t>
+        </is>
+      </c>
+      <c r="E47" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Derived Column create flow still works</t>
+        </is>
+      </c>
+      <c r="F47" s="75" t="inlineStr">
+        <is>
+          <t>Create a new Derived Column</t>
+        </is>
+      </c>
+      <c r="G47" s="75" t="inlineStr">
+        <is>
+          <t>Existing processing behavior works as before.</t>
+        </is>
+      </c>
+      <c r="H47" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I47" s="75" t="inlineStr"/>
+      <c r="J47" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K47" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L47" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M47" s="75" t="inlineStr"/>
+      <c r="N47" s="75" t="inlineStr">
+        <is>
+          <t>Create a new Derived Column</t>
+        </is>
+      </c>
+      <c r="O47" s="75" t="inlineStr">
+        <is>
+          <t>Create and submit column.</t>
+        </is>
+      </c>
+      <c r="P47" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1" s="67">
+      <c r="A48" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B48" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C48" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Derived Column edit flow still works</t>
+        </is>
+      </c>
+      <c r="D48" s="74" t="inlineStr">
+        <is>
+          <t>TC-46</t>
+        </is>
+      </c>
+      <c r="E48" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Derived Column edit flow still works</t>
+        </is>
+      </c>
+      <c r="F48" s="75" t="inlineStr">
+        <is>
+          <t>Existing Derived Column</t>
+        </is>
+      </c>
+      <c r="G48" s="75" t="inlineStr">
+        <is>
+          <t>Existing processing behavior works as before.</t>
+        </is>
+      </c>
+      <c r="H48" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I48" s="75" t="inlineStr"/>
+      <c r="J48" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K48" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L48" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M48" s="75" t="inlineStr"/>
+      <c r="N48" s="75" t="inlineStr">
+        <is>
+          <t>Existing Derived Column</t>
+        </is>
+      </c>
+      <c r="O48" s="75" t="inlineStr">
+        <is>
+          <t>Edit and submit column.</t>
+        </is>
+      </c>
+      <c r="P48" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1" s="67">
+      <c r="A49" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B49" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C49" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Lookup Column create flow still works</t>
+        </is>
+      </c>
+      <c r="D49" s="74" t="inlineStr">
+        <is>
+          <t>TC-47</t>
+        </is>
+      </c>
+      <c r="E49" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Lookup Column create flow still works</t>
+        </is>
+      </c>
+      <c r="F49" s="75" t="inlineStr">
+        <is>
+          <t>Create Lookup Column</t>
+        </is>
+      </c>
+      <c r="G49" s="75" t="inlineStr">
+        <is>
+          <t>Existing processing behavior works as before.</t>
+        </is>
+      </c>
+      <c r="H49" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I49" s="75" t="inlineStr"/>
+      <c r="J49" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K49" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L49" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M49" s="75" t="inlineStr"/>
+      <c r="N49" s="75" t="inlineStr">
+        <is>
+          <t>Create Lookup Column</t>
+        </is>
+      </c>
+      <c r="O49" s="75" t="inlineStr">
+        <is>
+          <t>Create and submit.</t>
+        </is>
+      </c>
+      <c r="P49" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="36" customHeight="1" s="67">
+      <c r="A50" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B50" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C50" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Lookup Column edit flow still works</t>
+        </is>
+      </c>
+      <c r="D50" s="74" t="inlineStr">
+        <is>
+          <t>TC-48</t>
+        </is>
+      </c>
+      <c r="E50" s="75" t="inlineStr">
+        <is>
+          <t>Verify existing Lookup Column edit flow still works</t>
+        </is>
+      </c>
+      <c r="F50" s="75" t="inlineStr">
+        <is>
+          <t>Existing Lookup Column</t>
+        </is>
+      </c>
+      <c r="G50" s="75" t="inlineStr">
+        <is>
+          <t>Existing processing behavior works as before.</t>
+        </is>
+      </c>
+      <c r="H50" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I50" s="75" t="inlineStr"/>
+      <c r="J50" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K50" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L50" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M50" s="75" t="inlineStr"/>
+      <c r="N50" s="75" t="inlineStr">
+        <is>
+          <t>Existing Lookup Column</t>
+        </is>
+      </c>
+      <c r="O50" s="75" t="inlineStr">
+        <is>
+          <t>Edit and submit.</t>
+        </is>
+      </c>
+      <c r="P50" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="36" customHeight="1" s="67">
+      <c r="A51" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B51" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C51" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh when stream contains only Derived Columns</t>
+        </is>
+      </c>
+      <c r="D51" s="74" t="inlineStr">
+        <is>
+          <t>TC-49</t>
+        </is>
+      </c>
+      <c r="E51" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh when stream contains only Derived Columns</t>
+        </is>
+      </c>
+      <c r="F51" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 2+ Derived Columns and no Lookup</t>
+        </is>
+      </c>
+      <c r="G51" s="75" t="inlineStr">
+        <is>
+          <t>Derived columns are processed successfully; Lookup count is 0.</t>
+        </is>
+      </c>
+      <c r="H51" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I51" s="75" t="inlineStr"/>
+      <c r="J51" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K51" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L51" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M51" s="75" t="inlineStr"/>
+      <c r="N51" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 2+ Derived Columns and no Lookup</t>
+        </is>
+      </c>
+      <c r="O51" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P51" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="36" customHeight="1" s="67">
+      <c r="A52" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B52" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-05</t>
+        </is>
+      </c>
+      <c r="C52" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh when stream contains only Lookup Columns</t>
+        </is>
+      </c>
+      <c r="D52" s="74" t="inlineStr">
+        <is>
+          <t>TC-50</t>
+        </is>
+      </c>
+      <c r="E52" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh when stream contains only Lookup Columns</t>
+        </is>
+      </c>
+      <c r="F52" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 2+ Lookup Columns and no Derived</t>
+        </is>
+      </c>
+      <c r="G52" s="75" t="inlineStr">
+        <is>
+          <t>Lookup columns are processed successfully; Derived count is 0.</t>
+        </is>
+      </c>
+      <c r="H52" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I52" s="75" t="inlineStr"/>
+      <c r="J52" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K52" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L52" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M52" s="75" t="inlineStr"/>
+      <c r="N52" s="75" t="inlineStr">
+        <is>
+          <t>Stream contains 2+ Lookup Columns and no Derived</t>
+        </is>
+      </c>
+      <c r="O52" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P52" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="36" customHeight="1" s="67">
+      <c r="A53" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B53" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C53" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh for single Derived Column</t>
+        </is>
+      </c>
+      <c r="D53" s="74" t="inlineStr">
+        <is>
+          <t>TC-51</t>
+        </is>
+      </c>
+      <c r="E53" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh for single Derived Column</t>
+        </is>
+      </c>
+      <c r="F53" s="75" t="inlineStr">
+        <is>
+          <t>Stream has exactly 1 Derived Column</t>
+        </is>
+      </c>
+      <c r="G53" s="75" t="inlineStr">
+        <is>
+          <t>Single Derived Column is processed successfully.</t>
+        </is>
+      </c>
+      <c r="H53" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I53" s="75" t="inlineStr"/>
+      <c r="J53" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K53" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L53" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M53" s="75" t="inlineStr"/>
+      <c r="N53" s="75" t="inlineStr">
+        <is>
+          <t>Stream has exactly 1 Derived Column</t>
+        </is>
+      </c>
+      <c r="O53" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P53" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="36" customHeight="1" s="67">
+      <c r="A54" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B54" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C54" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh for single Lookup Column</t>
+        </is>
+      </c>
+      <c r="D54" s="74" t="inlineStr">
+        <is>
+          <t>TC-52</t>
+        </is>
+      </c>
+      <c r="E54" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh for single Lookup Column</t>
+        </is>
+      </c>
+      <c r="F54" s="75" t="inlineStr">
+        <is>
+          <t>Stream has exactly 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="G54" s="75" t="inlineStr">
+        <is>
+          <t>Single Lookup Column is processed successfully.</t>
+        </is>
+      </c>
+      <c r="H54" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I54" s="75" t="inlineStr"/>
+      <c r="J54" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K54" s="74" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="L54" s="74" t="inlineStr">
+        <is>
+          <t>Minor</t>
+        </is>
+      </c>
+      <c r="M54" s="75" t="inlineStr"/>
+      <c r="N54" s="75" t="inlineStr">
+        <is>
+          <t>Stream has exactly 1 Lookup Column</t>
+        </is>
+      </c>
+      <c r="O54" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P54" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="36" customHeight="1" s="67">
+      <c r="A55" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B55" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C55" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh with zero records in Data Stream</t>
+        </is>
+      </c>
+      <c r="D55" s="74" t="inlineStr">
+        <is>
+          <t>TC-53</t>
+        </is>
+      </c>
+      <c r="E55" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh with zero records in Data Stream</t>
+        </is>
+      </c>
+      <c r="F55" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream exists but contains no records</t>
+        </is>
+      </c>
+      <c r="G55" s="75" t="inlineStr">
+        <is>
+          <t>Processing completes without error; counts reflect zero records processed/updated.</t>
+        </is>
+      </c>
+      <c r="H55" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I55" s="75" t="inlineStr"/>
+      <c r="J55" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K55" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L55" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M55" s="75" t="inlineStr"/>
+      <c r="N55" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream exists but contains no records</t>
+        </is>
+      </c>
+      <c r="O55" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P55" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="36" customHeight="1" s="67">
+      <c r="A56" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B56" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C56" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh with large dataset</t>
+        </is>
+      </c>
+      <c r="D56" s="74" t="inlineStr">
+        <is>
+          <t>TC-54</t>
+        </is>
+      </c>
+      <c r="E56" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh with large dataset</t>
+        </is>
+      </c>
+      <c r="F56" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream with large volume of records</t>
+        </is>
+      </c>
+      <c r="G56" s="75" t="inlineStr">
+        <is>
+          <t>Processing completes asynchronously without UI failure/time-out caused by synchronous processing.</t>
+        </is>
+      </c>
+      <c r="H56" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I56" s="75" t="inlineStr"/>
+      <c r="J56" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K56" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L56" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M56" s="75" t="inlineStr"/>
+      <c r="N56" s="75" t="inlineStr">
+        <is>
+          <t>Eligible stream with large volume of records</t>
+        </is>
+      </c>
+      <c r="O56" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P56" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="36" customHeight="1" s="67">
+      <c r="A57" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B57" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C57" s="75" t="inlineStr">
+        <is>
+          <t>Verify behavior when Derived/Lookup processing encounters invalid data</t>
+        </is>
+      </c>
+      <c r="D57" s="74" t="inlineStr">
+        <is>
+          <t>TC-55</t>
+        </is>
+      </c>
+      <c r="E57" s="75" t="inlineStr">
+        <is>
+          <t>Verify behavior when Derived/Lookup processing encounters invalid data</t>
+        </is>
+      </c>
+      <c r="F57" s="75" t="inlineStr">
+        <is>
+          <t>Dataset contains records that existing processing cannot calculate/resolve</t>
+        </is>
+      </c>
+      <c r="G57" s="75" t="inlineStr">
+        <is>
+          <t>Error handling follows existing Derived/Lookup processing behavior; unrelated records/columns are not incorrectly affected.</t>
+        </is>
+      </c>
+      <c r="H57" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I57" s="75" t="inlineStr"/>
+      <c r="J57" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K57" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L57" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M57" s="75" t="inlineStr"/>
+      <c r="N57" s="75" t="inlineStr">
+        <is>
+          <t>Dataset contains records that existing processing cannot calculate/resolve</t>
+        </is>
+      </c>
+      <c r="O57" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh.</t>
+        </is>
+      </c>
+      <c r="P57" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="36" customHeight="1" s="67">
+      <c r="A58" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B58" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C58" s="75" t="inlineStr">
+        <is>
+          <t>Verify action visibility updates after eligible column creation</t>
+        </is>
+      </c>
+      <c r="D58" s="74" t="inlineStr">
+        <is>
+          <t>TC-56</t>
+        </is>
+      </c>
+      <c r="E58" s="75" t="inlineStr">
+        <is>
+          <t>Verify action visibility updates after eligible column creation</t>
+        </is>
+      </c>
+      <c r="F58" s="75" t="inlineStr">
+        <is>
+          <t>Stream initially has no Derived/Lookup column</t>
+        </is>
+      </c>
+      <c r="G58" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns becomes available.</t>
+        </is>
+      </c>
+      <c r="H58" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I58" s="75" t="inlineStr"/>
+      <c r="J58" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K58" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L58" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M58" s="75" t="inlineStr"/>
+      <c r="N58" s="75" t="inlineStr">
+        <is>
+          <t>Stream initially has no Derived/Lookup column</t>
+        </is>
+      </c>
+      <c r="O58" s="75" t="inlineStr">
+        <is>
+          <t>1. Confirm action hidden.
+2. Create Derived Column.
+3. Return to Action menu.</t>
+        </is>
+      </c>
+      <c r="P58" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="36" customHeight="1" s="67">
+      <c r="A59" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B59" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C59" s="75" t="inlineStr">
+        <is>
+          <t>Verify action visibility updates after deleting all eligible columns</t>
+        </is>
+      </c>
+      <c r="D59" s="74" t="inlineStr">
+        <is>
+          <t>TC-57</t>
+        </is>
+      </c>
+      <c r="E59" s="75" t="inlineStr">
+        <is>
+          <t>Verify action visibility updates after deleting all eligible columns</t>
+        </is>
+      </c>
+      <c r="F59" s="75" t="inlineStr">
+        <is>
+          <t>Stream initially has Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="G59" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns is no longer displayed.</t>
+        </is>
+      </c>
+      <c r="H59" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I59" s="75" t="inlineStr"/>
+      <c r="J59" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K59" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L59" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M59" s="75" t="inlineStr"/>
+      <c r="N59" s="75" t="inlineStr">
+        <is>
+          <t>Stream initially has Derived/Lookup columns</t>
+        </is>
+      </c>
+      <c r="O59" s="75" t="inlineStr">
+        <is>
+          <t>1. Confirm action visible.
+2. Remove all Derived/Lookup columns.
+3. Open Action menu.</t>
+        </is>
+      </c>
+      <c r="P59" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="36" customHeight="1" s="67">
+      <c r="A60" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B60" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C60" s="75" t="inlineStr">
+        <is>
+          <t>Verify action remains hidden after deleting eligible columns from Key-Value stream</t>
+        </is>
+      </c>
+      <c r="D60" s="74" t="inlineStr">
+        <is>
+          <t>TC-58</t>
+        </is>
+      </c>
+      <c r="E60" s="75" t="inlineStr">
+        <is>
+          <t>Verify action remains hidden after deleting eligible columns from Key-Value stream</t>
+        </is>
+      </c>
+      <c r="F60" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value stream</t>
+        </is>
+      </c>
+      <c r="G60" s="75" t="inlineStr">
+        <is>
+          <t>Refresh Columns remains unavailable.</t>
+        </is>
+      </c>
+      <c r="H60" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I60" s="75" t="inlineStr"/>
+      <c r="J60" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K60" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L60" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M60" s="75" t="inlineStr"/>
+      <c r="N60" s="75" t="inlineStr">
+        <is>
+          <t>Key-Value stream</t>
+        </is>
+      </c>
+      <c r="O60" s="75" t="inlineStr">
+        <is>
+          <t>Remove/add eligible columns as applicable and reopen actions.</t>
+        </is>
+      </c>
+      <c r="P60" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="36" customHeight="1" s="67">
+      <c r="A61" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B61" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C61" s="75" t="inlineStr">
+        <is>
+          <t>Verify double-clicking Submit does not start duplicate processing</t>
+        </is>
+      </c>
+      <c r="D61" s="74" t="inlineStr">
+        <is>
+          <t>TC-59</t>
+        </is>
+      </c>
+      <c r="E61" s="75" t="inlineStr">
+        <is>
+          <t>Verify double-clicking Submit does not start duplicate processing</t>
+        </is>
+      </c>
+      <c r="F61" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="G61" s="75" t="inlineStr">
+        <is>
+          <t>Only one processing operation is initiated.</t>
+        </is>
+      </c>
+      <c r="H61" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I61" s="75" t="inlineStr"/>
+      <c r="J61" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K61" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L61" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M61" s="75" t="inlineStr"/>
+      <c r="N61" s="75" t="inlineStr">
+        <is>
+          <t>Confirmation modal open</t>
+        </is>
+      </c>
+      <c r="O61" s="75" t="inlineStr">
+        <is>
+          <t>Rapidly click Submit multiple times.</t>
+        </is>
+      </c>
+      <c r="P61" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="36" customHeight="1" s="67">
+      <c r="A62" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B62" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-06</t>
+        </is>
+      </c>
+      <c r="C62" s="75" t="inlineStr">
+        <is>
+          <t>Verify refreshing the page during processing does not corrupt processing state</t>
+        </is>
+      </c>
+      <c r="D62" s="74" t="inlineStr">
+        <is>
+          <t>TC-60</t>
+        </is>
+      </c>
+      <c r="E62" s="75" t="inlineStr">
+        <is>
+          <t>Verify refreshing the page during processing does not corrupt processing state</t>
+        </is>
+      </c>
+      <c r="F62" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is running</t>
+        </is>
+      </c>
+      <c r="G62" s="75" t="inlineStr">
+        <is>
+          <t>Backend processing continues according to existing async behavior; no duplicate process is created.</t>
+        </is>
+      </c>
+      <c r="H62" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I62" s="75" t="inlineStr"/>
+      <c r="J62" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K62" s="74" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="L62" s="74" t="inlineStr">
+        <is>
+          <t>Major</t>
+        </is>
+      </c>
+      <c r="M62" s="75" t="inlineStr"/>
+      <c r="N62" s="75" t="inlineStr">
+        <is>
+          <t>Refresh is running</t>
+        </is>
+      </c>
+      <c r="O62" s="75" t="inlineStr">
+        <is>
+          <t>Refresh browser/page.</t>
+        </is>
+      </c>
+      <c r="P62" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="36" customHeight="1" s="67">
+      <c r="A63" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B63" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-07</t>
+        </is>
+      </c>
+      <c r="C63" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion modal values are actual and not hardcoded</t>
+        </is>
+      </c>
+      <c r="D63" s="74" t="inlineStr">
+        <is>
+          <t>TC-61</t>
+        </is>
+      </c>
+      <c r="E63" s="75" t="inlineStr">
+        <is>
+          <t>Verify completion modal values are actual and not hardcoded</t>
+        </is>
+      </c>
+      <c r="F63" s="75" t="inlineStr">
+        <is>
+          <t>Use different datasets/column counts</t>
+        </is>
+      </c>
+      <c r="G63" s="75" t="inlineStr">
+        <is>
+          <t>Completion values change according to actual processing result.</t>
+        </is>
+      </c>
+      <c r="H63" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I63" s="75" t="inlineStr"/>
+      <c r="J63" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K63" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L63" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M63" s="75" t="inlineStr"/>
+      <c r="N63" s="75" t="inlineStr">
+        <is>
+          <t>Use different datasets/column counts</t>
+        </is>
+      </c>
+      <c r="O63" s="75" t="inlineStr">
+        <is>
+          <t>Trigger multiple refreshes with different counts/outcomes.</t>
+        </is>
+      </c>
+      <c r="P63" s="74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="36" customHeight="1" s="67">
+      <c r="A64" s="74" t="inlineStr">
+        <is>
+          <t>VIS-REF-COL</t>
+        </is>
+      </c>
+      <c r="B64" s="74" t="inlineStr">
+        <is>
+          <t>TS-REF-07</t>
+        </is>
+      </c>
+      <c r="C64" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh does not affect another stream's computed values</t>
+        </is>
+      </c>
+      <c r="D64" s="74" t="inlineStr">
+        <is>
+          <t>TC-62</t>
+        </is>
+      </c>
+      <c r="E64" s="75" t="inlineStr">
+        <is>
+          <t>Verify refresh does not affect another stream's computed values</t>
+        </is>
+      </c>
+      <c r="F64" s="75" t="inlineStr">
+        <is>
+          <t>A and B have different source data and calculated results</t>
+        </is>
+      </c>
+      <c r="G64" s="75" t="inlineStr">
+        <is>
+          <t>B's Derived/Lookup values remain unchanged.</t>
+        </is>
+      </c>
+      <c r="H64" s="74" t="inlineStr">
+        <is>
+          <t>To Test</t>
+        </is>
+      </c>
+      <c r="I64" s="75" t="inlineStr"/>
+      <c r="J64" s="74" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="K64" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="L64" s="74" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="M64" s="75" t="inlineStr"/>
+      <c r="N64" s="75" t="inlineStr">
+        <is>
+          <t>A and B have different source data and calculated results</t>
+        </is>
+      </c>
+      <c r="O64" s="75" t="inlineStr">
+        <is>
+          <t>Trigger refresh only on A.</t>
+        </is>
+      </c>
+      <c r="P64" s="74" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
